--- a/data/processed/Template CGRI.xlsx
+++ b/data/processed/Template CGRI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arzumkarahan/Desktop/DSBA/2nd year/Geopolitics/Group Project/company-geopolitical-risk-index/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439467C4-65B8-9D4A-B536-2F2C4B48D0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB1CEC0-A852-1842-8950-07C275203FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{266D4EF2-EDBA-FA44-A696-554C257F20B6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{266D4EF2-EDBA-FA44-A696-554C257F20B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -1553,8 +1553,53 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1589,53 +1634,8 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3990,37 +3990,35 @@
       <sheetName val="Country of Revenues - Toyota"/>
       <sheetName val="Country of Revenues - TSMC"/>
       <sheetName val="Country of Revenues - VW"/>
-      <sheetName val="Revenue Exposure"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4060,37 +4058,35 @@
       <sheetName val="Country of Suppliers - Samsung"/>
       <sheetName val="Country of Suppliers - Amazon"/>
       <sheetName val="Country of Suppliers - Ford"/>
-      <sheetName val="Supply Chain Exposure"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4629,42 +4625,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="100"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="115"/>
     </row>
     <row r="2" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
       <c r="O2" s="28"/>
       <c r="P2" s="28"/>
       <c r="Q2" s="28"/>
@@ -4799,19 +4795,19 @@
       <c r="R8" s="36"/>
     </row>
     <row r="9" spans="1:19" ht="25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
       <c r="L9" s="37"/>
       <c r="M9" s="37"/>
       <c r="N9" s="37"/>
@@ -4821,12 +4817,12 @@
       <c r="R9" s="38"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
       <c r="E10" s="37"/>
       <c r="F10" s="37"/>
       <c r="G10" s="37"/>
@@ -4843,10 +4839,10 @@
       <c r="R10" s="38"/>
     </row>
     <row r="11" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="103"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
@@ -4883,17 +4879,17 @@
       <c r="R12" s="49"/>
     </row>
     <row r="13" spans="1:19" ht="22" x14ac:dyDescent="0.3">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
       <c r="J13" s="50"/>
       <c r="K13" s="50"/>
       <c r="L13" s="50"/>
@@ -4945,24 +4941,24 @@
       <c r="R15" s="49"/>
     </row>
     <row r="16" spans="1:19" ht="22" x14ac:dyDescent="0.3">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="103" t="s">
         <v>146</v>
       </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="108"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="108"/>
-      <c r="P16" s="108"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="104"/>
       <c r="Q16" s="48"/>
       <c r="R16" s="49"/>
     </row>
@@ -5007,26 +5003,26 @@
       <c r="R18" s="49"/>
     </row>
     <row r="19" spans="1:32" ht="22" x14ac:dyDescent="0.3">
-      <c r="A19" s="107" t="s">
+      <c r="A19" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="108"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="117"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="105"/>
     </row>
     <row r="20" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="51"/>
@@ -5111,23 +5107,23 @@
       <c r="R23" s="41"/>
     </row>
     <row r="24" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="118"/>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="119"/>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
+      <c r="A24" s="106"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="107"/>
+      <c r="M24" s="107"/>
+      <c r="N24" s="107"/>
+      <c r="O24" s="107"/>
+      <c r="P24" s="107"/>
+      <c r="Q24" s="107"/>
       <c r="R24" s="54"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
@@ -5145,164 +5141,164 @@
       <c r="AF24" s="4"/>
     </row>
     <row r="25" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="121"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="121"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="121"/>
-      <c r="P25" s="121"/>
-      <c r="Q25" s="121"/>
-      <c r="R25" s="122"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="110"/>
     </row>
     <row r="26" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="120"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="121"/>
-      <c r="J26" s="121"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="121"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="121"/>
-      <c r="P26" s="121"/>
-      <c r="Q26" s="121"/>
-      <c r="R26" s="122"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="109"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="109"/>
+      <c r="M26" s="109"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="109"/>
+      <c r="P26" s="109"/>
+      <c r="Q26" s="109"/>
+      <c r="R26" s="110"/>
     </row>
     <row r="27" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="110"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="110"/>
-      <c r="R27" s="111"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="96"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="96"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="97"/>
     </row>
     <row r="28" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="109"/>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="110"/>
-      <c r="P28" s="110"/>
-      <c r="Q28" s="110"/>
-      <c r="R28" s="111"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="97"/>
     </row>
     <row r="29" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="109"/>
-      <c r="B29" s="110"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="110"/>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="110"/>
-      <c r="R29" s="111"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="97"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" s="112" t="s">
+      <c r="A30" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="113"/>
-      <c r="C30" s="113"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="113"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="113"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="113"/>
-      <c r="N30" s="113"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="113"/>
-      <c r="Q30" s="113"/>
-      <c r="R30" s="114"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="99"/>
+      <c r="N30" s="99"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="99"/>
+      <c r="R30" s="100"/>
     </row>
     <row r="31" spans="1:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="115"/>
-      <c r="B31" s="115"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="115"/>
-      <c r="N31" s="115"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="115"/>
-      <c r="Q31" s="115"/>
-      <c r="R31" s="116"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="101"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="101"/>
+      <c r="Q31" s="101"/>
+      <c r="R31" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A10:D11"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A27:R29"/>
     <mergeCell ref="A30:R31"/>
     <mergeCell ref="A16:P16"/>
     <mergeCell ref="A19:R19"/>
     <mergeCell ref="A24:Q24"/>
     <mergeCell ref="A25:R26"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A13:I13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5329,17 +5325,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
       <c r="E1" s="94"/>
-      <c r="F1" s="95" t="s">
+      <c r="F1" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
       <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5397,8 +5393,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H3" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.2329977178729381</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.2341629210672878</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5430,8 +5426,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H4" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>4.20040509952522</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>4.1224201273946832</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5463,8 +5459,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H5" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.3492023453852702</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.3527009387433941</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -5496,8 +5492,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H6" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.3708271672512238</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.3370317187938516</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5529,8 +5525,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H7" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.9423810394738572</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.9590017074492954</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5562,8 +5558,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H8" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.3623470485532048</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.3659147915694292</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5595,8 +5591,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H9" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.5146561371664067</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.5101763308337643</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -5628,8 +5624,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H10" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.6108798837735678</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.5735273258773814</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5661,8 +5657,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H11" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.7381580746102783</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.7031493026055951</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5694,8 +5690,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H12" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>2.714839155854162</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>2.7014553727535269</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5727,8 +5723,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H13" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.1862337233911346</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.1689434997969013</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -5760,8 +5756,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H14" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>2.922946008700579</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>2.927222753446685</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -5793,8 +5789,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H15" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.8689896052884483</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.8259774068860732</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -5826,8 +5822,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H16" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.0111654637861411</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>2.9406831938015419</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -5859,8 +5855,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H17" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.8043721298581952</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.7603096388070711</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -5892,8 +5888,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H18" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.1054044035090187</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.0913553768712871</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -5925,8 +5921,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H19" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>5.646494063119821</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>5.5404198631744634</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5958,8 +5954,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H20" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.2333252749144665</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.2143833396415848</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -5991,8 +5987,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H21" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.1143484151847991</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.1077680719530325</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6024,8 +6020,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H22" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.242332808890394</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.2191176467995981</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6057,8 +6053,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H23" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>4.7016474234051842</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>4.6123039334998115</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6090,8 +6086,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H24" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.2967671490720662</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.3049083714544709</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6123,8 +6119,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H25" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>3.0895514355683051</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>3.0635163871469113</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6156,8 +6152,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H26" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>4.1359178283459732</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>4.0539948771988161</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6189,8 +6185,8 @@
         <v>0.9348282637706109</v>
       </c>
       <c r="H27" s="13">
-        <f>(0.15*Tabella6[[#This Row],[HQ Country Risk]]+0.45*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
-        <v>2.9045955305767293</v>
+        <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]]+0.4*Tabella6[[#This Row],[Revenue Exposure]]+0.4*Tabella6[[#This Row],[Supply Chain Exposure]])*Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]]</f>
+        <v>2.9042897821266824</v>
       </c>
     </row>
   </sheetData>
@@ -61758,18 +61754,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61791,18 +61787,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6D44B9-BFA0-496F-91FF-88181837C605}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D57F7E9-094C-4E40-AC1D-B397B1E486C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6D44B9-BFA0-496F-91FF-88181837C605}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/processed/Template CGRI.xlsx
+++ b/data/processed/Template CGRI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bocconi.sharepoint.com/sites/Geopolitics-DataGroup1/Documenti condivisi/General/Final Dataset - CGPR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arzumkarahan/Desktop/DSBA/2nd year/Geopolitics/Group Project/company-geopolitical-risk-index/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="13_ncr:1_{265C54AE-AA66-4A4A-B31A-5CCC79B2EC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54642838-D8D9-9145-AA13-B4D1865249F2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E492AAA3-9195-9241-8D5F-7EB55BF1857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="8" xr2:uid="{266D4EF2-EDBA-FA44-A696-554C257F20B6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" firstSheet="1" activeTab="2" xr2:uid="{266D4EF2-EDBA-FA44-A696-554C257F20B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="174">
   <si>
     <t>Corporate Geopolitical Risk Index - INTRODUCTION</t>
   </si>
@@ -749,9 +749,6 @@
     </r>
   </si>
   <si>
-    <t>Totale Energies</t>
-  </si>
-  <si>
     <t>Leonardo</t>
   </si>
   <si>
@@ -833,9 +830,6 @@
     <t>ExxonMobil</t>
   </si>
   <si>
-    <t>TotaleEnergies</t>
-  </si>
-  <si>
     <t>Revenue Exposure - Final Component</t>
   </si>
   <si>
@@ -843,9 +837,6 @@
   </si>
   <si>
     <t>Financial Exposure - Multiplier</t>
-  </si>
-  <si>
-    <t>TotalEnergies</t>
   </si>
   <si>
     <r>
@@ -877,7 +868,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1078,6 +1069,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -1574,7 +1571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1654,6 +1651,48 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1741,59 +1780,216 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="50">
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2019,6 +2215,77 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2201,6 +2468,19 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2277,6 +2557,16 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2462,304 +2752,6 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4137,6 +4129,122 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Revenue Exposure - Overall"/>
+      <sheetName val="HHI Index Submultiplier"/>
+      <sheetName val="Country of Revenues - Apple"/>
+      <sheetName val="Country of Revenues - Leonardo"/>
+      <sheetName val="Country of Revenues - Prysmian"/>
+      <sheetName val="Country of Revenues - Pfizer"/>
+      <sheetName val="Country of Revenues - Unicredit"/>
+      <sheetName val="Country of Revenues - Campari"/>
+      <sheetName val="Country of Revenues - Moncler"/>
+      <sheetName val="Country of Revenues - Ferrari"/>
+      <sheetName val="Country of Revenues - Alibaba"/>
+      <sheetName val="Country of Revenues - Nestlè"/>
+      <sheetName val="Country of Revenues - Gazprom"/>
+      <sheetName val="Country of Revenues - Novartis"/>
+      <sheetName val="Country of Revenues - Moderna"/>
+      <sheetName val="Country of Revenues - HSBC"/>
+      <sheetName val="Country of Revenues - Walmart"/>
+      <sheetName val="Country of Revenues - Unilever"/>
+      <sheetName val="Country of Revenues - Coca-Cola"/>
+      <sheetName val="Country of Revenues - CAT"/>
+      <sheetName val="Country of Revenues - Tesla"/>
+      <sheetName val="Country of Revenues - Alphabet"/>
+      <sheetName val="Country of Revenues - S.Aramco"/>
+      <sheetName val="Country of Revenues - Shell"/>
+      <sheetName val="Country of Revenues - Chevron"/>
+      <sheetName val="Country of Revenues - Exxon"/>
+      <sheetName val="Country of Revenues - Meta"/>
+      <sheetName val="Country of Revenues - Microsoft"/>
+      <sheetName val="Country of Revenues - Ford"/>
+      <sheetName val="Country of Revenues - P&amp;G"/>
+      <sheetName val="Country of Revenues - Samsung"/>
+      <sheetName val="Country of Revenues - Amazon"/>
+      <sheetName val="Country of Revenues - NVIDIA"/>
+      <sheetName val="Country of Revenues - Allianz"/>
+      <sheetName val="Country of Revenues - ASML"/>
+      <sheetName val="Country of Revenues - BNP"/>
+      <sheetName val="Country of Revenues - Eli LIlly"/>
+      <sheetName val="Country of Revenues - ENI"/>
+      <sheetName val="Country of Revenues - JP Morgan"/>
+      <sheetName val="Country of Revenues - Oreal"/>
+      <sheetName val="Country of Revenues - LVMH"/>
+      <sheetName val="Country of Revenues - Nordisk"/>
+      <sheetName val="Country of Revenues - Reliance"/>
+      <sheetName val="Country of Revenues - SAP"/>
+      <sheetName val="Country of Revenues - Sony"/>
+      <sheetName val="Country of Revenues - Tencent"/>
+      <sheetName val="Country of Revenues - Total En"/>
+      <sheetName val="Country of Revenues - Toyota"/>
+      <sheetName val="Country of Revenues - TSMC"/>
+      <sheetName val="Country of Revenues - VW"/>
+      <sheetName val="Revenue Exposure"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+      <sheetData sheetId="48"/>
+      <sheetData sheetId="49"/>
+      <sheetData sheetId="50" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls driveId="b!l_n03KDCVkiW9MtcnL3APRVbGYFs-pNBkfIzIC1YCDr9ZBrEumVuSoAEit5Mj9s5" itemId="01W5IV7QVZOIFGYEIIZRALDXIQ42QEHEOL">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
@@ -4191,6 +4299,7 @@
       <sheetName val="Country of Suppliers - Samsung"/>
       <sheetName val="Country of Suppliers - Amazon"/>
       <sheetName val="Country of Suppliers - Ford"/>
+      <sheetName val="Supply Chain Exposure"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -4243,120 +4352,7 @@
       <sheetData sheetId="47"/>
       <sheetData sheetId="48"/>
       <sheetData sheetId="49"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Revenue Exposure - Overall"/>
-      <sheetName val="HHI Index Submultiplier"/>
-      <sheetName val="Country of Revenues - Apple"/>
-      <sheetName val="Country of Revenues - Leonardo"/>
-      <sheetName val="Country of Revenues - Prysmian"/>
-      <sheetName val="Country of Revenues - Pfizer"/>
-      <sheetName val="Country of Revenues - Unicredit"/>
-      <sheetName val="Country of Revenues - Campari"/>
-      <sheetName val="Country of Revenues - Moncler"/>
-      <sheetName val="Country of Revenues - Ferrari"/>
-      <sheetName val="Country of Revenues - Alibaba"/>
-      <sheetName val="Country of Revenues - Nestlè"/>
-      <sheetName val="Country of Revenues - Gazprom"/>
-      <sheetName val="Country of Revenues - Novartis"/>
-      <sheetName val="Country of Revenues - Moderna"/>
-      <sheetName val="Country of Revenues - HSBC"/>
-      <sheetName val="Country of Revenues - Walmart"/>
-      <sheetName val="Country of Revenues - Unilever"/>
-      <sheetName val="Country of Revenues - Coca-Cola"/>
-      <sheetName val="Country of Revenues - CAT"/>
-      <sheetName val="Country of Revenues - Tesla"/>
-      <sheetName val="Country of Revenues - Alphabet"/>
-      <sheetName val="Country of Revenues - S.Aramco"/>
-      <sheetName val="Country of Revenues - Shell"/>
-      <sheetName val="Country of Revenues - Chevron"/>
-      <sheetName val="Country of Revenues - Exxon"/>
-      <sheetName val="Country of Revenues - Meta"/>
-      <sheetName val="Country of Revenues - Microsoft"/>
-      <sheetName val="Country of Revenues - Ford"/>
-      <sheetName val="Country of Revenues - P&amp;G"/>
-      <sheetName val="Country of Revenues - Samsung"/>
-      <sheetName val="Country of Revenues - Amazon"/>
-      <sheetName val="Country of Revenues - NVIDIA"/>
-      <sheetName val="Country of Revenues - Allianz"/>
-      <sheetName val="Country of Revenues - ASML"/>
-      <sheetName val="Country of Revenues - BNP"/>
-      <sheetName val="Country of Revenues - Eli LIlly"/>
-      <sheetName val="Country of Revenues - ENI"/>
-      <sheetName val="Country of Revenues - JP Morgan"/>
-      <sheetName val="Country of Revenues - Oreal"/>
-      <sheetName val="Country of Revenues - LVMH"/>
-      <sheetName val="Country of Revenues - Nordisk"/>
-      <sheetName val="Country of Revenues - Reliance"/>
-      <sheetName val="Country of Revenues - SAP"/>
-      <sheetName val="Country of Revenues - Sony"/>
-      <sheetName val="Country of Revenues - Tencent"/>
-      <sheetName val="Country of Revenues - Total En"/>
-      <sheetName val="Country of Revenues - Toyota"/>
-      <sheetName val="Country of Revenues - TSMC"/>
-      <sheetName val="Country of Revenues - VW"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
+      <sheetData sheetId="50" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4371,7 +4367,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{114D04B0-DFA9-2641-BC93-63E24476E166}" name="Company Name" dataDxfId="47"/>
     <tableColumn id="2" xr3:uid="{390C4C5F-17E3-5745-9D43-52AECD0F68D0}" name="HQ Country Risk" dataDxfId="46">
-      <calculatedColumnFormula>'HQ Country Risk'!D2</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F4DC2280-B3B7-8143-9EEB-D90E84A367A6}" name="Revenue Exposure" dataDxfId="45">
       <calculatedColumnFormula>'Revenue Exposure'!B2</calculatedColumnFormula>
@@ -4394,15 +4390,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{83501AF2-7068-A64B-9751-BBC380B17425}" name="Tabella15" displayName="Tabella15" ref="A1:D49" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{83501AF2-7068-A64B-9751-BBC380B17425}" name="Tabella15" displayName="Tabella15" ref="A1:D49" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:D49" xr:uid="{83501AF2-7068-A64B-9751-BBC380B17425}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B38435E5-96BE-094A-8C52-CD51E7663F3A}" name="Company Name" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{3020DBDE-A108-A44C-B71F-936CC56F40B2}" name="HQ Country" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{A5551044-D5F5-5949-8678-5EDAE3383FFD}" name="Country Geopolitical Risk Index" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{B38435E5-96BE-094A-8C52-CD51E7663F3A}" name="Company Name" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{3020DBDE-A108-A44C-B71F-936CC56F40B2}" name="HQ Country" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{A5551044-D5F5-5949-8678-5EDAE3383FFD}" name="Country Geopolitical Risk Index" dataDxfId="36">
       <calculatedColumnFormula>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F0036FF1-FD7A-4149-B6BC-7E7A90FA5FD5}" name="HQ Country Risk - Component" dataDxfId="16">
+    <tableColumn id="4" xr3:uid="{F0036FF1-FD7A-4149-B6BC-7E7A90FA5FD5}" name="HQ Country Risk - Component" dataDxfId="35">
       <calculatedColumnFormula>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4411,15 +4407,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{76BB8A42-43EE-154F-97F4-4CB478CC6758}" name="Tabella7" displayName="Tabella7" ref="A1:B49" totalsRowShown="0" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{76BB8A42-43EE-154F-97F4-4CB478CC6758}" name="Tabella7" displayName="Tabella7" ref="A1:B49" totalsRowShown="0" tableBorderDxfId="34">
   <autoFilter ref="A1:B49" xr:uid="{76BB8A42-43EE-154F-97F4-4CB478CC6758}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
     <sortCondition ref="A1:A26"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C41DD8CD-4E04-E54A-AAD2-0AF392B640A4}" name="Company Name" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{2E9378D4-70A0-7143-A77C-CE7608813C88}" name="Revenue Exposure - Final Component" dataDxfId="14">
-      <calculatedColumnFormula>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{C41DD8CD-4E04-E54A-AAD2-0AF392B640A4}" name="Company Name" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{2E9378D4-70A0-7143-A77C-CE7608813C88}" name="Revenue Exposure - Final Component" dataDxfId="32">
+      <calculatedColumnFormula>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4427,15 +4423,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F0F8D28A-684A-7147-A5A4-D17ACFA8B479}" name="Tabella8" displayName="Tabella8" ref="A1:B49" totalsRowShown="0" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F0F8D28A-684A-7147-A5A4-D17ACFA8B479}" name="Tabella8" displayName="Tabella8" ref="A1:B49" totalsRowShown="0" dataDxfId="31">
   <autoFilter ref="A1:B49" xr:uid="{F0F8D28A-684A-7147-A5A4-D17ACFA8B479}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
     <sortCondition ref="A1:A26"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7CCBD08B-A76A-A543-8D03-3BBEA51248D9}" name="Company Name" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{B166E128-2A16-014E-8A4D-DAA9AFA70404}" name="Supply Chain Exposure - Final Component" dataDxfId="12">
-      <calculatedColumnFormula>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{7CCBD08B-A76A-A543-8D03-3BBEA51248D9}" name="Company Name" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{B166E128-2A16-014E-8A4D-DAA9AFA70404}" name="Supply Chain Exposure - Final Component" dataDxfId="29">
+      <calculatedColumnFormula>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4443,15 +4439,15 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C86FC93B-CBAD-6643-AF20-94EE2506DD66}" name="Tabella110" displayName="Tabella110" ref="A1:C49" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C86FC93B-CBAD-6643-AF20-94EE2506DD66}" name="Tabella110" displayName="Tabella110" ref="A1:C49" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="A1:C49" xr:uid="{C86FC93B-CBAD-6643-AF20-94EE2506DD66}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
     <sortCondition ref="A1:A26"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{86EAEBEB-F8FD-AD43-9EC0-FF384E73F7E5}" name="Company" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{FA89D168-1F6C-404B-A3E2-35F75B765F61}" name="Net Debt/EBITDA 2024" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{6400FC17-87D0-C24E-8E32-236541B8EF44}" name="Financial Exposure - Multiplier" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{86EAEBEB-F8FD-AD43-9EC0-FF384E73F7E5}" name="Company" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{FA89D168-1F6C-404B-A3E2-35F75B765F61}" name="Net Debt/EBITDA 2024" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{6400FC17-87D0-C24E-8E32-236541B8EF44}" name="Financial Exposure - Multiplier" dataDxfId="24">
       <calculatedColumnFormula xml:space="preserve"> IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;0, 0.8,IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;2, 0.9, IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]] &lt; 4, 1,IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;6,1.1,1.2))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4460,35 +4456,33 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC1FFDE3-E73D-F34F-AD9F-E79C098A1189}" name="Tabella14" displayName="Tabella14" ref="A4:B57" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DC1FFDE3-E73D-F34F-AD9F-E79C098A1189}" name="Tabella14" displayName="Tabella14" ref="A4:B57" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A4:B57" xr:uid="{DC1FFDE3-E73D-F34F-AD9F-E79C098A1189}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:B57">
     <sortCondition ref="A5:A57"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4E635AAD-6014-E148-AA49-974B1E858237}" name="Sector - List" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{92E21896-74AD-0B4A-BD90-518C9AFFDB88}" name="S&amp;P Global Industry Risk Assessment Index" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{4E635AAD-6014-E148-AA49-974B1E858237}" name="Sector - List" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{92E21896-74AD-0B4A-BD90-518C9AFFDB88}" name="S&amp;P Global Industry Risk Assessment Index" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E7DF17DF-2645-FC4C-AA3C-411E43797A20}" name="Tabella2" displayName="Tabella2" ref="D4:H52" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E7DF17DF-2645-FC4C-AA3C-411E43797A20}" name="Tabella2" displayName="Tabella2" ref="D4:H52" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="D4:H52" xr:uid="{E7DF17DF-2645-FC4C-AA3C-411E43797A20}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D5:H29">
     <sortCondition ref="D4:D29"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5F3336B4-1546-DC42-AE03-2774D6965BD7}" name="Company Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{728E570B-D233-4440-A07D-CF8D41BF7CC7}" name="Sector" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{BABFC70B-4541-7243-A082-E9074A88D9C2}" name="S&amp;P Global Industry Risk Assessment" dataDxfId="2">
-      <calculatedColumnFormula xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{F994125E-30A5-4F4A-B988-1EB10694824A}" name="S&amp;P Global Industry Risk Assessment - Value" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{5F3336B4-1546-DC42-AE03-2774D6965BD7}" name="Company Name" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{728E570B-D233-4440-A07D-CF8D41BF7CC7}" name="Sector" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{BABFC70B-4541-7243-A082-E9074A88D9C2}" name="S&amp;P Global Industry Risk Assessment" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{F994125E-30A5-4F4A-B988-1EB10694824A}" name="S&amp;P Global Industry Risk Assessment - Value" dataDxfId="14">
       <calculatedColumnFormula>IF(F5="Very low risk",1,IF(F5="Low risk",2,IF(F5="Intermediate risk",3,IF(F5="Moderately high risk",4,IF(F5="High risk",5,IF(F5="Very high risk",6, ""))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8651B97A-DDE7-DD4A-8F49-555D65246A21}" name="Sector Risk - Multiplier" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{8651B97A-DDE7-DD4A-8F49-555D65246A21}" name="Sector Risk - Multiplier" dataDxfId="13">
       <calculatedColumnFormula>IF(F5="Very low risk",0.75,IF(F5="Low risk",0.85,IF(F5="Intermediate risk",1,IF(F5="Moderately high risk",1.1,IF(F5="High risk",1.15,IF(F5="Very high risk",1.25, ""))))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4497,31 +4491,31 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21C084FF-6AE8-AC41-BBCA-DDA3AB28EBC8}" name="Tabella1" displayName="Tabella1" ref="A4:B6526" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21C084FF-6AE8-AC41-BBCA-DDA3AB28EBC8}" name="Tabella1" displayName="Tabella1" ref="A4:B6526" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
   <autoFilter ref="A4:B6526" xr:uid="{21C084FF-6AE8-AC41-BBCA-DDA3AB28EBC8}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9E64E2B8-8E7C-0C49-AB72-0739369D456C}" name="Observation Date" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{A8EB1197-2AE8-4443-83B6-8F63AD146E1B}" name="VIX" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{9E64E2B8-8E7C-0C49-AB72-0739369D456C}" name="Observation Date" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{A8EB1197-2AE8-4443-83B6-8F63AD146E1B}" name="VIX" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07FFB839-5F71-ED41-A209-53E6FAAE7096}" name="Tabella3" displayName="Tabella3" ref="D4:H29" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07FFB839-5F71-ED41-A209-53E6FAAE7096}" name="Tabella3" displayName="Tabella3" ref="D4:H29" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="D4:H29" xr:uid="{07FFB839-5F71-ED41-A209-53E6FAAE7096}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{94D22EF3-4773-304D-9942-E367DA2EFF19}" name="Year" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{D429AE48-E46C-234E-86C5-6398C39A99AF}" name="VIX" dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{94D22EF3-4773-304D-9942-E367DA2EFF19}" name="Year" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D429AE48-E46C-234E-86C5-6398C39A99AF}" name="VIX" dataDxfId="3">
       <calculatedColumnFormula>AVERAGEIFS($B$5:$B$6526,$A$5:$A$6526,"&gt;="&amp;DATE(D5,1,1),$A$5:$A$6526,"&lt;="&amp;DATE(D5,12,31))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1E0FA3BA-80B9-E040-B18F-AADA16338E4C}" name="VIX Average" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{1E0FA3BA-80B9-E040-B18F-AADA16338E4C}" name="VIX Average" dataDxfId="2">
       <calculatedColumnFormula>AVERAGE(Tabella3[VIX])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2636A586-7DBB-0C4A-BA3D-94F92362E4F8}" name="Delta %" dataDxfId="23">
+    <tableColumn id="4" xr3:uid="{2636A586-7DBB-0C4A-BA3D-94F92362E4F8}" name="Delta %" dataDxfId="1">
       <calculatedColumnFormula>(Tabella3[[#This Row],[VIX]]-Tabella3[[#This Row],[VIX Average]])/Tabella3[[#This Row],[VIX Average]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1077B055-A5D0-1D49-AAF9-19DAE124D828}" name="Volatility Risk - Multiplier ( 1 + Delta %)" dataDxfId="22">
+    <tableColumn id="5" xr3:uid="{1077B055-A5D0-1D49-AAF9-19DAE124D828}" name="Volatility Risk - Multiplier ( 1 + Delta %)" dataDxfId="0">
       <calculatedColumnFormula xml:space="preserve"> 1 +0.3*Tabella3[[#This Row],[Delta %]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4860,42 +4854,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="78"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="112"/>
     </row>
     <row r="2" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
       <c r="O2" s="24"/>
       <c r="P2" s="24"/>
       <c r="Q2" s="24"/>
@@ -4946,7 +4940,7 @@
     </row>
     <row r="5" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
@@ -5030,19 +5024,19 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:19" ht="25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
       <c r="L9" s="33"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
@@ -5052,12 +5046,12 @@
       <c r="R9" s="34"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
       <c r="E10" s="33"/>
       <c r="F10" s="33"/>
       <c r="G10" s="33"/>
@@ -5074,10 +5068,10 @@
       <c r="R10" s="34"/>
     </row>
     <row r="11" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
@@ -5114,17 +5108,17 @@
       <c r="R12" s="45"/>
     </row>
     <row r="13" spans="1:19" ht="22" x14ac:dyDescent="0.3">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="119" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120"/>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
       <c r="L13" s="46"/>
@@ -5176,24 +5170,24 @@
       <c r="R15" s="45"/>
     </row>
     <row r="16" spans="1:19" ht="22" x14ac:dyDescent="0.3">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="119" t="s">
         <v>141</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="86"/>
-      <c r="O16" s="86"/>
-      <c r="P16" s="86"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
       <c r="Q16" s="44"/>
       <c r="R16" s="45"/>
     </row>
@@ -5238,26 +5232,26 @@
       <c r="R18" s="45"/>
     </row>
     <row r="19" spans="1:32" ht="22" x14ac:dyDescent="0.3">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="86"/>
-      <c r="O19" s="86"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="86"/>
-      <c r="R19" s="95"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="129"/>
     </row>
     <row r="20" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47"/>
@@ -5342,23 +5336,23 @@
       <c r="R23" s="37"/>
     </row>
     <row r="24" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="96"/>
-      <c r="B24" s="97"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="97"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="97"/>
-      <c r="Q24" s="97"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="131"/>
       <c r="R24" s="50"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
@@ -5376,150 +5370,150 @@
       <c r="AF24" s="4"/>
     </row>
     <row r="25" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="98" t="s">
+      <c r="A25" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="99"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="100"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="133"/>
+      <c r="I25" s="133"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
+      <c r="N25" s="133"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="134"/>
     </row>
     <row r="26" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="100"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="133"/>
+      <c r="I26" s="133"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
+      <c r="N26" s="133"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="133"/>
+      <c r="Q26" s="133"/>
+      <c r="R26" s="134"/>
     </row>
     <row r="27" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="88"/>
-      <c r="P27" s="88"/>
-      <c r="Q27" s="88"/>
-      <c r="R27" s="89"/>
+      <c r="B27" s="122"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="122"/>
+      <c r="J27" s="122"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="122"/>
+      <c r="R27" s="123"/>
     </row>
     <row r="28" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="88"/>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="88"/>
-      <c r="R28" s="89"/>
+      <c r="A28" s="121"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="122"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="122"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="123"/>
     </row>
     <row r="29" spans="1:32" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="87"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="88"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="88"/>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="89"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="122"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122"/>
+      <c r="I29" s="122"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="122"/>
+      <c r="R29" s="123"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="91"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91"/>
-      <c r="M30" s="91"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="91"/>
-      <c r="P30" s="91"/>
-      <c r="Q30" s="91"/>
-      <c r="R30" s="92"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="125"/>
+      <c r="N30" s="125"/>
+      <c r="O30" s="125"/>
+      <c r="P30" s="125"/>
+      <c r="Q30" s="125"/>
+      <c r="R30" s="126"/>
     </row>
     <row r="31" spans="1:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="93"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="93"/>
-      <c r="P31" s="93"/>
-      <c r="Q31" s="93"/>
-      <c r="R31" s="94"/>
+      <c r="A31" s="127"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="127"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="127"/>
+      <c r="N31" s="127"/>
+      <c r="O31" s="127"/>
+      <c r="P31" s="127"/>
+      <c r="Q31" s="127"/>
+      <c r="R31" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5560,17 +5554,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
       <c r="E1" s="72"/>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
       <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5604,8 +5598,8 @@
         <v>19</v>
       </c>
       <c r="B3" s="12">
-        <f>'HQ Country Risk'!D2</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.42</v>
       </c>
       <c r="C3" s="12">
         <f>'Revenue Exposure'!B2</f>
@@ -5629,7 +5623,7 @@
       </c>
       <c r="H3" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.376686838161755</v>
+        <v>3.2341629210672878</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5637,7 +5631,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="12">
-        <f>'HQ Country Risk'!D3</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C4" s="12">
@@ -5670,7 +5664,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="12">
-        <f>'HQ Country Risk'!D4</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C5" s="12">
@@ -5703,8 +5697,8 @@
         <v>22</v>
       </c>
       <c r="B6" s="12">
-        <f>'HQ Country Risk'!D5</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.59</v>
       </c>
       <c r="C6" s="12">
         <f>'Revenue Exposure'!B5</f>
@@ -5728,7 +5722,7 @@
       </c>
       <c r="H6" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.4357495834480294</v>
+        <v>3.3370317187938521</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5736,8 +5730,8 @@
         <v>23</v>
       </c>
       <c r="B7" s="12">
-        <f>'HQ Country Risk'!D6</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.65</v>
       </c>
       <c r="C7" s="12">
         <f>'Revenue Exposure'!B6</f>
@@ -5761,7 +5755,7 @@
       </c>
       <c r="H7" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>4.0811650649588378</v>
+        <v>3.9590017074492949</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5769,8 +5763,8 @@
         <v>24</v>
       </c>
       <c r="B8" s="12">
-        <f>'HQ Country Risk'!D7</f>
-        <v>3.57</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C8" s="12">
         <f>'Revenue Exposure'!B7</f>
@@ -5794,7 +5788,7 @@
       </c>
       <c r="H8" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.2673838925680072</v>
+        <v>3.3659147915694292</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5802,8 +5796,8 @@
         <v>25</v>
       </c>
       <c r="B9" s="12">
-        <f>'HQ Country Risk'!D8</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.84</v>
       </c>
       <c r="C9" s="12">
         <f>'Revenue Exposure'!B8</f>
@@ -5827,7 +5821,7 @@
       </c>
       <c r="H9" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.5749599295130681</v>
+        <v>3.5101763308337648</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -5835,7 +5829,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="12">
-        <f>'HQ Country Risk'!D9</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C10" s="12">
@@ -5868,8 +5862,8 @@
         <v>27</v>
       </c>
       <c r="B11" s="12">
-        <f>'HQ Country Risk'!D10</f>
-        <v>3.42</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C11" s="12">
         <f>'Revenue Exposure'!B10</f>
@@ -5893,7 +5887,7 @@
       </c>
       <c r="H11" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.576461376299402</v>
+        <v>3.7031493026055951</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5901,7 +5895,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="12">
-        <f>'HQ Country Risk'!D11</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.65</v>
       </c>
       <c r="C12" s="12">
@@ -5934,7 +5928,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="12">
-        <f>'HQ Country Risk'!D12</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.65</v>
       </c>
       <c r="C13" s="12">
@@ -5967,8 +5961,8 @@
         <v>30</v>
       </c>
       <c r="B14" s="12">
-        <f>'HQ Country Risk'!D13</f>
-        <v>3.2</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C14" s="12">
         <f>'Revenue Exposure'!B13</f>
@@ -5992,7 +5986,7 @@
       </c>
       <c r="H14" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>2.7791459564654208</v>
+        <v>2.9272227534466855</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -6000,8 +5994,8 @@
         <v>31</v>
       </c>
       <c r="B15" s="12">
-        <f>'HQ Country Risk'!D14</f>
-        <v>5.07</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C15" s="12">
         <f>'Revenue Exposure'!B14</f>
@@ -6025,7 +6019,7 @@
       </c>
       <c r="H15" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.9740542038673383</v>
+        <v>3.8259774068860737</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -6033,8 +6027,8 @@
         <v>32</v>
       </c>
       <c r="B16" s="12">
-        <f>'HQ Country Risk'!D15</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.2</v>
       </c>
       <c r="C16" s="12">
         <f>'Revenue Exposure'!B15</f>
@@ -6058,7 +6052,7 @@
       </c>
       <c r="H16" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.0822816309148764</v>
+        <v>2.9406831938015423</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6066,8 +6060,8 @@
         <v>33</v>
       </c>
       <c r="B17" s="12">
-        <f>'HQ Country Risk'!D16</f>
-        <v>3.38</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C17" s="12">
         <f>'Revenue Exposure'!B16</f>
@@ -6091,7 +6085,7 @@
       </c>
       <c r="H17" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.6270405215239334</v>
+        <v>3.7603096388070716</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6099,8 +6093,8 @@
         <v>34</v>
       </c>
       <c r="B18" s="12">
-        <f>'HQ Country Risk'!D17</f>
-        <v>4.26</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C18" s="12">
         <f>'Revenue Exposure'!B17</f>
@@ -6124,7 +6118,7 @@
       </c>
       <c r="H18" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.10136738757627</v>
+        <v>3.0913553768712871</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6132,8 +6126,8 @@
         <v>35</v>
       </c>
       <c r="B19" s="12">
-        <f>'HQ Country Risk'!D18</f>
-        <v>3.65</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>5.07</v>
       </c>
       <c r="C19" s="12">
         <f>'Revenue Exposure'!B18</f>
@@ -6157,7 +6151,7 @@
       </c>
       <c r="H19" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>5.2775835485327169</v>
+        <v>5.5404198631744626</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -6165,8 +6159,8 @@
         <v>36</v>
       </c>
       <c r="B20" s="12">
-        <f>'HQ Country Risk'!D19</f>
-        <v>3.38</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.57</v>
       </c>
       <c r="C20" s="12">
         <f>'Revenue Exposure'!B19</f>
@@ -6190,7 +6184,7 @@
       </c>
       <c r="H20" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.1831226825010952</v>
+        <v>3.2143833396415844</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6198,8 +6192,8 @@
         <v>37</v>
       </c>
       <c r="B21" s="12">
-        <f>'HQ Country Risk'!D20</f>
-        <v>4.26</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C21" s="12">
         <f>'Revenue Exposure'!B20</f>
@@ -6223,7 +6217,7 @@
       </c>
       <c r="H21" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.1182381485072637</v>
+        <v>3.107768071953033</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6231,8 +6225,8 @@
         <v>38</v>
       </c>
       <c r="B22" s="12">
-        <f>'HQ Country Risk'!D21</f>
-        <v>3.42</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.38</v>
       </c>
       <c r="C22" s="12">
         <f>'Revenue Exposure'!B21</f>
@@ -6256,7 +6250,7 @@
       </c>
       <c r="H22" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.2258484102987466</v>
+        <v>3.2191176467995981</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6264,8 +6258,8 @@
         <v>39</v>
       </c>
       <c r="B23" s="12">
-        <f>'HQ Country Risk'!D22</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.26</v>
       </c>
       <c r="C23" s="12">
         <f>'Revenue Exposure'!B22</f>
@@ -6289,7 +6283,7 @@
       </c>
       <c r="H23" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>4.6005250973763028</v>
+        <v>4.6123039334998115</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6297,8 +6291,8 @@
         <v>40</v>
       </c>
       <c r="B24" s="12">
-        <f>'HQ Country Risk'!D23</f>
-        <v>3.59</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.65</v>
       </c>
       <c r="C24" s="12">
         <f>'Revenue Exposure'!B23</f>
@@ -6322,7 +6316,7 @@
       </c>
       <c r="H24" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.2938026116808765</v>
+        <v>3.3049083714544709</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6330,8 +6324,8 @@
         <v>41</v>
       </c>
       <c r="B25" s="12">
-        <f>'HQ Country Risk'!D24</f>
-        <v>3.65</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.38</v>
       </c>
       <c r="C25" s="12">
         <f>'Revenue Exposure'!B24</f>
@@ -6355,7 +6349,7 @@
       </c>
       <c r="H25" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>3.1079394262412903</v>
+        <v>3.0635163871469113</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6363,8 +6357,8 @@
         <v>42</v>
       </c>
       <c r="B26" s="12">
-        <f>'HQ Country Risk'!D25</f>
-        <v>4.1900000000000004</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>4.26</v>
       </c>
       <c r="C26" s="12">
         <f>'Revenue Exposure'!B25</f>
@@ -6388,7 +6382,7 @@
       </c>
       <c r="H26" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>4.0424777929891622</v>
+        <v>4.0539948771988161</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6396,8 +6390,8 @@
         <v>43</v>
       </c>
       <c r="B27" s="12">
-        <f>'HQ Country Risk'!D26</f>
-        <v>3.84</v>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
+        <v>3.42</v>
       </c>
       <c r="C27" s="12">
         <f>'Revenue Exposure'!B26</f>
@@ -6421,15 +6415,15 @@
       </c>
       <c r="H27" s="13">
         <f>(0.2*Tabella6[[#This Row],[HQ Country Risk]] + 0.4 *Tabella6[[#This Row],[Revenue Exposure]] + 0.4 *Tabella6[[#This Row],[Supply Chain Exposure]])*(Tabella6[[#This Row],[Financial Exposure]]*Tabella6[[#This Row],[Sector Risk]]*Tabella6[[#This Row],[Volatility Risk]])</f>
-        <v>2.9733922873846059</v>
+        <v>2.9042897821266824</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="130" t="s">
-        <v>144</v>
+      <c r="A28" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="B28" s="12">
-        <f>'HQ Country Risk'!D27</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C28" s="12">
@@ -6440,7 +6434,7 @@
         <f>'Supply Chain Exposure'!B27</f>
         <v>3.933599781021683</v>
       </c>
-      <c r="E28" s="129">
+      <c r="E28" s="1">
         <f>'Financial Exposure'!C27</f>
         <v>0.9</v>
       </c>
@@ -6458,11 +6452,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="130" t="s">
-        <v>145</v>
+      <c r="A29" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B29" s="12">
-        <f>'HQ Country Risk'!D28</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C29" s="12">
@@ -6473,7 +6467,7 @@
         <f>'Supply Chain Exposure'!B28</f>
         <v>3.8211898948381755</v>
       </c>
-      <c r="E29" s="129">
+      <c r="E29" s="1">
         <f>'Financial Exposure'!C28</f>
         <v>0.9</v>
       </c>
@@ -6491,11 +6485,11 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="130" t="s">
-        <v>146</v>
+      <c r="A30" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B30" s="12">
-        <f>'HQ Country Risk'!D29</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C30" s="12">
@@ -6506,7 +6500,7 @@
         <f>'Supply Chain Exposure'!B29</f>
         <v>3.8568532687503554</v>
       </c>
-      <c r="E30" s="129">
+      <c r="E30" s="1">
         <f>'Financial Exposure'!C29</f>
         <v>1</v>
       </c>
@@ -6524,11 +6518,11 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="130" t="s">
-        <v>147</v>
+      <c r="A31" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="B31" s="12">
-        <f>'HQ Country Risk'!D30</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C31" s="12">
@@ -6539,7 +6533,7 @@
         <f>'Supply Chain Exposure'!B30</f>
         <v>3.705888348945964</v>
       </c>
-      <c r="E31" s="129">
+      <c r="E31" s="1">
         <f>'Financial Exposure'!C30</f>
         <v>1</v>
       </c>
@@ -6557,11 +6551,11 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="130" t="s">
-        <v>148</v>
+      <c r="A32" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="B32" s="12">
-        <f>'HQ Country Risk'!D31</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C32" s="12">
@@ -6572,7 +6566,7 @@
         <f>'Supply Chain Exposure'!B31</f>
         <v>4.403895166962764</v>
       </c>
-      <c r="E32" s="129">
+      <c r="E32" s="1">
         <f>'Financial Exposure'!C31</f>
         <v>1</v>
       </c>
@@ -6590,11 +6584,11 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="130" t="s">
-        <v>149</v>
+      <c r="A33" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="B33" s="12">
-        <f>'HQ Country Risk'!D32</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C33" s="12">
@@ -6605,7 +6599,7 @@
         <f>'Supply Chain Exposure'!B32</f>
         <v>4.2165249705618049</v>
       </c>
-      <c r="E33" s="129">
+      <c r="E33" s="1">
         <f>'Financial Exposure'!C32</f>
         <v>0.9</v>
       </c>
@@ -6623,11 +6617,11 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="130" t="s">
-        <v>150</v>
+      <c r="A34" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="B34" s="12">
-        <f>'HQ Country Risk'!D33</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.84</v>
       </c>
       <c r="C34" s="12">
@@ -6638,7 +6632,7 @@
         <f>'Supply Chain Exposure'!B33</f>
         <v>3.7417976563578033</v>
       </c>
-      <c r="E34" s="129">
+      <c r="E34" s="1">
         <f>'Financial Exposure'!C33</f>
         <v>0.9</v>
       </c>
@@ -6656,11 +6650,11 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="130" t="s">
-        <v>151</v>
+      <c r="A35" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B35" s="12">
-        <f>'HQ Country Risk'!D34</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.26</v>
       </c>
       <c r="C35" s="12">
@@ -6671,7 +6665,7 @@
         <f>'Supply Chain Exposure'!B34</f>
         <v>4.5950509503610713</v>
       </c>
-      <c r="E35" s="129">
+      <c r="E35" s="1">
         <f>'Financial Exposure'!C34</f>
         <v>0.9</v>
       </c>
@@ -6689,11 +6683,11 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="130" t="s">
-        <v>152</v>
+      <c r="A36" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B36" s="12">
-        <f>'HQ Country Risk'!D35</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>2.78</v>
       </c>
       <c r="C36" s="12">
@@ -6704,7 +6698,7 @@
         <f>'Supply Chain Exposure'!B35</f>
         <v>4.1058377293294797</v>
       </c>
-      <c r="E36" s="129">
+      <c r="E36" s="1">
         <f>'Financial Exposure'!C35</f>
         <v>1</v>
       </c>
@@ -6722,11 +6716,11 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="130" t="s">
-        <v>154</v>
+      <c r="A37" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="B37" s="12">
-        <f>'HQ Country Risk'!D36</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>5.96</v>
       </c>
       <c r="C37" s="12">
@@ -6737,7 +6731,7 @@
         <f>'Supply Chain Exposure'!B36</f>
         <v>6.1593393427174998</v>
       </c>
-      <c r="E37" s="129">
+      <c r="E37" s="1">
         <f>'Financial Exposure'!C36</f>
         <v>0.9</v>
       </c>
@@ -6755,11 +6749,11 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="130" t="s">
-        <v>156</v>
+      <c r="A38" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B38" s="12">
-        <f>'HQ Country Risk'!D37</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>2.78</v>
       </c>
       <c r="C38" s="12">
@@ -6770,7 +6764,7 @@
         <f>'Supply Chain Exposure'!B37</f>
         <v>3.9736869583125203</v>
       </c>
-      <c r="E38" s="129">
+      <c r="E38" s="1">
         <f>'Financial Exposure'!C37</f>
         <v>0.9</v>
       </c>
@@ -6788,11 +6782,11 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="130" t="s">
-        <v>157</v>
+      <c r="A39" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="B39" s="12">
-        <f>'HQ Country Risk'!D38</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C39" s="12">
@@ -6803,7 +6797,7 @@
         <f>'Supply Chain Exposure'!B38</f>
         <v>4.3655765807730429</v>
       </c>
-      <c r="E39" s="129">
+      <c r="E39" s="1">
         <f>'Financial Exposure'!C38</f>
         <v>0.9</v>
       </c>
@@ -6821,11 +6815,11 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="130" t="s">
-        <v>158</v>
+      <c r="A40" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="B40" s="12">
-        <f>'HQ Country Risk'!D39</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.32</v>
       </c>
       <c r="C40" s="12">
@@ -6836,7 +6830,7 @@
         <f>'Supply Chain Exposure'!B39</f>
         <v>4.4086778766527672</v>
       </c>
-      <c r="E40" s="129">
+      <c r="E40" s="1">
         <f>'Financial Exposure'!C39</f>
         <v>1.1000000000000001</v>
       </c>
@@ -6854,11 +6848,11 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="130" t="s">
-        <v>160</v>
+      <c r="A41" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="B41" s="12">
-        <f>'HQ Country Risk'!D40</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C41" s="12">
@@ -6869,7 +6863,7 @@
         <f>'Supply Chain Exposure'!B40</f>
         <v>4.6380416946562937</v>
       </c>
-      <c r="E41" s="129">
+      <c r="E41" s="1">
         <f>'Financial Exposure'!C40</f>
         <v>0.9</v>
       </c>
@@ -6887,11 +6881,11 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="130" t="s">
-        <v>161</v>
+      <c r="A42" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="B42" s="12">
-        <f>'HQ Country Risk'!D41</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.32</v>
       </c>
       <c r="C42" s="12">
@@ -6902,7 +6896,7 @@
         <f>'Supply Chain Exposure'!B41</f>
         <v>4.1490866159605329</v>
       </c>
-      <c r="E42" s="129">
+      <c r="E42" s="1">
         <f>'Financial Exposure'!C41</f>
         <v>1</v>
       </c>
@@ -6920,11 +6914,11 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="130" t="s">
-        <v>162</v>
+      <c r="A43" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="B43" s="12">
-        <f>'HQ Country Risk'!D42</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C43" s="12">
@@ -6935,7 +6929,7 @@
         <f>'Supply Chain Exposure'!B42</f>
         <v>4.1509408526411349</v>
       </c>
-      <c r="E43" s="129">
+      <c r="E43" s="1">
         <f>'Financial Exposure'!C42</f>
         <v>1</v>
       </c>
@@ -6953,11 +6947,11 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="130" t="s">
-        <v>163</v>
+      <c r="A44" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="B44" s="12">
-        <f>'HQ Country Risk'!D43</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C44" s="12">
@@ -6968,7 +6962,7 @@
         <f>'Supply Chain Exposure'!B43</f>
         <v>4.1203082258415957</v>
       </c>
-      <c r="E44" s="129">
+      <c r="E44" s="1">
         <f>'Financial Exposure'!C43</f>
         <v>0.9</v>
       </c>
@@ -6986,11 +6980,11 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="130" t="s">
-        <v>164</v>
+      <c r="A45" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="B45" s="12">
-        <f>'HQ Country Risk'!D44</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C45" s="12">
@@ -7001,7 +6995,7 @@
         <f>'Supply Chain Exposure'!B44</f>
         <v>4.0604725450576815</v>
       </c>
-      <c r="E45" s="129">
+      <c r="E45" s="1">
         <f>'Financial Exposure'!C44</f>
         <v>0.9</v>
       </c>
@@ -7019,11 +7013,11 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="130" t="s">
-        <v>165</v>
+      <c r="A46" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="B46" s="12">
-        <f>'HQ Country Risk'!D45</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C46" s="12">
@@ -7034,7 +7028,7 @@
         <f>'Supply Chain Exposure'!B45</f>
         <v>4.0222762327087151</v>
       </c>
-      <c r="E46" s="129">
+      <c r="E46" s="1">
         <f>'Financial Exposure'!C45</f>
         <v>0.9</v>
       </c>
@@ -7052,11 +7046,11 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="130" t="s">
-        <v>166</v>
+      <c r="A47" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="B47" s="12">
-        <f>'HQ Country Risk'!D46</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.42</v>
       </c>
       <c r="C47" s="12">
@@ -7067,7 +7061,7 @@
         <f>'Supply Chain Exposure'!B46</f>
         <v>3.6502319459771546</v>
       </c>
-      <c r="E47" s="129">
+      <c r="E47" s="1">
         <f>'Financial Exposure'!C46</f>
         <v>0.9</v>
       </c>
@@ -7085,11 +7079,11 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="130" t="s">
-        <v>168</v>
+      <c r="A48" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="B48" s="12">
-        <f>'HQ Country Risk'!D47</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>3.32</v>
       </c>
       <c r="C48" s="12">
@@ -7100,7 +7094,7 @@
         <f>'Supply Chain Exposure'!B47</f>
         <v>3.9813161648332605</v>
       </c>
-      <c r="E48" s="129">
+      <c r="E48" s="1">
         <f>'Financial Exposure'!C47</f>
         <v>0.9</v>
       </c>
@@ -7118,11 +7112,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="130" t="s">
-        <v>169</v>
+      <c r="A49" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="B49" s="12">
-        <f>'HQ Country Risk'!D48</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C49" s="12">
@@ -7133,7 +7127,7 @@
         <f>'Supply Chain Exposure'!B48</f>
         <v>3.965095709003819</v>
       </c>
-      <c r="E49" s="129">
+      <c r="E49" s="1">
         <f>'Financial Exposure'!C48</f>
         <v>0.9</v>
       </c>
@@ -7151,11 +7145,11 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="130" t="s">
-        <v>170</v>
+      <c r="A50" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="B50" s="12">
-        <f>'HQ Country Risk'!D49</f>
+        <f>INDEX(Tabella15[HQ Country Risk - Component], MATCH(Tabella6[[#This Row],[Company Name]], Tabella15[Company Name], 0))</f>
         <v>4.1900000000000004</v>
       </c>
       <c r="C50" s="12">
@@ -7166,7 +7160,7 @@
         <f>'Supply Chain Exposure'!B49</f>
         <v>4.0692615675076942</v>
       </c>
-      <c r="E50" s="129">
+      <c r="E50" s="1">
         <f>'Financial Exposure'!C49</f>
         <v>0.9</v>
       </c>
@@ -7270,7 +7264,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="56">
-        <v>4.1900000000000004</v>
+        <v>3.42</v>
       </c>
       <c r="C2" s="56">
         <v>3.3948194835522369</v>
@@ -7289,16 +7283,16 @@
       </c>
       <c r="H2" s="14">
         <f>(M$10*B2+M$11*C2+M$12*D2)*E2*F2*G2</f>
-        <v>3.5216602061234719</v>
+        <v>3.2227128967452314</v>
       </c>
       <c r="J2" s="69"/>
       <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="138" t="s">
+      <c r="L2" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="138" t="s">
+      <c r="M2" s="103" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7326,9 +7320,9 @@
       </c>
       <c r="H3" s="14">
         <f t="shared" ref="H3:H49" si="0">(M$10*B3+M$11*C3+M$12*D3)*E3*F3*G3</f>
-        <v>3.9333883227708899</v>
-      </c>
-      <c r="J3" s="140" t="s">
+        <v>4.0208826001939508</v>
+      </c>
+      <c r="J3" s="105" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="64" cm="1">
@@ -7337,11 +7331,11 @@
       </c>
       <c r="L3" s="64" cm="1">
         <f t="array" ref="L3">CORREL(_xlfn._xlws.FILTER($B2:$B26,ISNUMBER($B2:$B26)*ISNUMBER(C2:C26)),_xlfn._xlws.FILTER(C2:C26,ISNUMBER($B2:$B26)*ISNUMBER(C2:C26)))</f>
-        <v>0.18676586526787997</v>
+        <v>0.70782220278160224</v>
       </c>
       <c r="M3" s="64" cm="1">
         <f t="array" ref="M3">CORREL(_xlfn._xlws.FILTER($B2:$B26,ISNUMBER($B2:$B26)*ISNUMBER(D2:D26)),_xlfn._xlws.FILTER(D2:D26,ISNUMBER($B2:$B26)*ISNUMBER(D2:D26)))</f>
-        <v>3.4933851818152666E-2</v>
+        <v>0.69763034438709437</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -7368,14 +7362,14 @@
       </c>
       <c r="H4" s="14">
         <f t="shared" si="0"/>
-        <v>3.3783268501620318</v>
-      </c>
-      <c r="J4" s="140" t="s">
+        <v>3.3684702523635695</v>
+      </c>
+      <c r="J4" s="105" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="64" cm="1">
         <f t="array" ref="K4">CORREL(_xlfn._xlws.FILTER($C2:$C26,ISNUMBER($C2:$C26)*ISNUMBER(B2:B26)),_xlfn._xlws.FILTER(B2:B26,ISNUMBER($C2:$C26)*ISNUMBER(B2:B26)))</f>
-        <v>0.18676586526787997</v>
+        <v>0.70782220278160224</v>
       </c>
       <c r="L4" s="64" cm="1">
         <f t="array" ref="L4">CORREL(_xlfn._xlws.FILTER($C2:$C26,ISNUMBER($C2:$C26)*ISNUMBER(C2:C26)),_xlfn._xlws.FILTER(C2:C26,ISNUMBER($C2:$C26)*ISNUMBER(C2:C26)))</f>
@@ -7391,7 +7385,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="9">
-        <v>4.1900000000000004</v>
+        <v>3.59</v>
       </c>
       <c r="C5" s="9">
         <v>4.4116251089083942</v>
@@ -7410,14 +7404,14 @@
       </c>
       <c r="H5" s="14">
         <f t="shared" si="0"/>
-        <v>3.4342448146375593</v>
-      </c>
-      <c r="J5" s="140" t="s">
+        <v>3.2722459749873338</v>
+      </c>
+      <c r="J5" s="105" t="s">
         <v>14</v>
       </c>
       <c r="K5" s="64" cm="1">
         <f t="array" ref="K5">CORREL(_xlfn._xlws.FILTER($D2:$D26,ISNUMBER($D2:$D26)*ISNUMBER(B2:B26)),_xlfn._xlws.FILTER(B2:B26,ISNUMBER($D2:$D26)*ISNUMBER(B2:B26)))</f>
-        <v>3.4933851818152666E-2</v>
+        <v>0.69763034438709437</v>
       </c>
       <c r="L5" s="64" cm="1">
         <f t="array" ref="L5">CORREL(_xlfn._xlws.FILTER($D2:$D26,ISNUMBER($D2:$D26)*ISNUMBER(C2:C26)),_xlfn._xlws.FILTER(C2:C26,ISNUMBER($D2:$D26)*ISNUMBER(C2:C26)))</f>
@@ -7433,7 +7427,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="56">
-        <v>4.1900000000000004</v>
+        <v>3.65</v>
       </c>
       <c r="C6" s="56">
         <v>3.3561259320403041</v>
@@ -7452,7 +7446,7 @@
       </c>
       <c r="H6" s="14">
         <f t="shared" si="0"/>
-        <v>4.2710709604998236</v>
+        <v>3.98769454479255</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -7460,7 +7454,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="9">
-        <v>3.57</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C7" s="9">
         <v>4.1002007312436222</v>
@@ -7479,7 +7473,7 @@
       </c>
       <c r="H7" s="14">
         <f t="shared" si="0"/>
-        <v>3.1478147302039647</v>
+        <v>3.3599385827499604</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -7487,7 +7481,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="56">
-        <v>4.1900000000000004</v>
+        <v>3.84</v>
       </c>
       <c r="C8" s="56">
         <v>3.9368104426669146</v>
@@ -7506,7 +7500,7 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
-        <v>3.657558724560674</v>
+        <v>3.5173152753368133</v>
       </c>
       <c r="J8" s="70"/>
       <c r="K8" s="58" t="s">
@@ -7540,16 +7534,16 @@
       </c>
       <c r="H9" s="14">
         <f t="shared" si="0"/>
-        <v>3.5235325017242536</v>
+        <v>3.5514130729374713</v>
       </c>
       <c r="J9" s="69"/>
       <c r="K9" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="L9" s="138" t="s">
+      <c r="L9" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="139" t="s">
+      <c r="M9" s="104" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7558,7 +7552,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="56">
-        <v>3.42</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C10" s="56">
         <v>5.041123077931009</v>
@@ -7577,22 +7571,22 @@
       </c>
       <c r="H10" s="14">
         <f t="shared" si="0"/>
-        <v>3.3506345794421173</v>
-      </c>
-      <c r="J10" s="140" t="s">
+        <v>3.6595362976433665</v>
+      </c>
+      <c r="J10" s="105" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="64">
         <f>SUM(K3:M3)</f>
-        <v>1.2216997170860324</v>
+        <v>2.4054525471686965</v>
       </c>
       <c r="L10" s="64">
         <f>1/K10</f>
-        <v>0.81853174394209971</v>
-      </c>
-      <c r="M10" s="141">
+        <v>0.41572218964661584</v>
+      </c>
+      <c r="M10" s="106">
         <f>L10/SUM(L$10:L$12)</f>
-        <v>0.42729479692197553</v>
+        <v>0.33449412867363482</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -7619,22 +7613,22 @@
       </c>
       <c r="H11" s="14">
         <f t="shared" si="0"/>
-        <v>2.6718898542223735</v>
-      </c>
-      <c r="J11" s="140" t="s">
+        <v>2.6859106438867744</v>
+      </c>
+      <c r="J11" s="105" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="64">
         <f>SUM(K4:M4)</f>
-        <v>1.9020898661490915</v>
+        <v>2.4231462036628137</v>
       </c>
       <c r="L11" s="64">
         <f>1/K11</f>
-        <v>0.52573751524399159</v>
-      </c>
-      <c r="M11" s="141">
+        <v>0.41268661316779226</v>
+      </c>
+      <c r="M11" s="106">
         <f>L11/SUM(L$10:L$12)</f>
-        <v>0.27444861665173986</v>
+        <v>0.33205167423027354</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -7661,22 +7655,22 @@
       </c>
       <c r="H12" s="14">
         <f t="shared" si="0"/>
-        <v>3.1357751554086355</v>
-      </c>
-      <c r="J12" s="140" t="s">
+        <v>3.1521493470546207</v>
+      </c>
+      <c r="J12" s="105" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="64">
         <f>SUM(K5:M5)</f>
-        <v>1.7502578526993644</v>
+        <v>2.4129543452683064</v>
       </c>
       <c r="L12" s="64">
         <f>1/K12</f>
-        <v>0.57134438703287826</v>
-      </c>
-      <c r="M12" s="141">
+        <v>0.41442972261823124</v>
+      </c>
+      <c r="M12" s="106">
         <f>L12/SUM(L$10:L$12)</f>
-        <v>0.29825658642628455</v>
+        <v>0.3334541970960917</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -7684,7 +7678,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="9">
-        <v>3.2</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C13" s="9">
         <v>4.0756275288239578</v>
@@ -7703,7 +7697,7 @@
       </c>
       <c r="H13" s="14">
         <f t="shared" si="0"/>
-        <v>2.6653765974799923</v>
+        <v>2.9616673072031023</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -7711,7 +7705,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="56">
-        <v>5.07</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C14" s="56">
         <v>5.2124622727051149</v>
@@ -7730,7 +7724,7 @@
       </c>
       <c r="H14" s="14">
         <f t="shared" si="0"/>
-        <v>4.0453631773182144</v>
+        <v>3.7747384291101995</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -7738,7 +7732,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="9">
-        <v>4.1900000000000004</v>
+        <v>3.2</v>
       </c>
       <c r="C15" s="9">
         <v>5.1711360861675111</v>
@@ -7757,7 +7751,7 @@
       </c>
       <c r="H15" s="14">
         <f t="shared" si="0"/>
-        <v>3.0437451361529591</v>
+        <v>2.8301992753779732</v>
       </c>
       <c r="J15" s="63"/>
     </row>
@@ -7766,7 +7760,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="56">
-        <v>3.38</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C16" s="56">
         <v>5.2612344608866266</v>
@@ -7785,7 +7779,7 @@
       </c>
       <c r="H16" s="14">
         <f t="shared" si="0"/>
-        <v>3.3748841396301055</v>
+        <v>3.7069332217182156</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7793,7 +7787,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="9">
-        <v>4.26</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C17" s="9">
         <v>4.5829008442437091</v>
@@ -7812,7 +7806,7 @@
       </c>
       <c r="H17" s="14">
         <f t="shared" si="0"/>
-        <v>3.0819166602784871</v>
+        <v>3.0751727043328585</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -7820,7 +7814,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="56">
-        <v>3.65</v>
+        <v>5.07</v>
       </c>
       <c r="C18" s="56">
         <v>7.3623067404550397</v>
@@ -7839,7 +7833,7 @@
       </c>
       <c r="H18" s="14">
         <f t="shared" si="0"/>
-        <v>4.712612531146557</v>
+        <v>5.3963280094798476</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -7847,7 +7841,7 @@
         <v>36</v>
       </c>
       <c r="B19" s="9">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="C19" s="9">
         <v>4.0305108185247978</v>
@@ -7866,7 +7860,7 @@
       </c>
       <c r="H19" s="14">
         <f t="shared" si="0"/>
-        <v>3.0679850516612772</v>
+        <v>3.1676813893513667</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -7874,7 +7868,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="56">
-        <v>4.26</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="C20" s="56">
         <v>4.3659773288524724</v>
@@ -7893,7 +7887,7 @@
       </c>
       <c r="H20" s="14">
         <f t="shared" si="0"/>
-        <v>3.1335602396638493</v>
+        <v>3.1118717464751797</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -7901,7 +7895,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="9">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="C21" s="9">
         <v>3.9318580373530141</v>
@@ -7920,7 +7914,7 @@
       </c>
       <c r="H21" s="14">
         <f t="shared" si="0"/>
-        <v>3.1269650500812851</v>
+        <v>3.1560181944152812</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7928,7 +7922,7 @@
         <v>39</v>
       </c>
       <c r="B22" s="56">
-        <v>4.1900000000000004</v>
+        <v>4.26</v>
       </c>
       <c r="C22" s="56">
         <v>6.3838241971610312</v>
@@ -7947,7 +7941,7 @@
       </c>
       <c r="H22" s="14">
         <f t="shared" si="0"/>
-        <v>4.28307259769191</v>
+        <v>4.4387464180027454</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7955,7 +7949,7 @@
         <v>40</v>
       </c>
       <c r="B23" s="9">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="C23" s="9">
         <v>3.4740648625929329</v>
@@ -7974,7 +7968,7 @@
       </c>
       <c r="H23" s="14">
         <f t="shared" si="0"/>
-        <v>3.3036496948274259</v>
+        <v>3.3172969105055432</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7982,7 +7976,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="56">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="C24" s="56">
         <v>4.0129565213980154</v>
@@ -8001,7 +7995,7 @@
       </c>
       <c r="H24" s="14">
         <f t="shared" si="0"/>
-        <v>3.074054117017865</v>
+        <v>3.01571105889367</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -8009,7 +8003,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="9">
-        <v>4.1900000000000004</v>
+        <v>4.26</v>
       </c>
       <c r="C25" s="9">
         <v>6.2516869498945535</v>
@@ -8028,7 +8022,7 @@
       </c>
       <c r="H25" s="14">
         <f t="shared" si="0"/>
-        <v>3.8506078120627363</v>
+        <v>3.9602778271135892</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -8036,7 +8030,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="56">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="C26" s="56">
         <v>3.4274332673491497</v>
@@ -8055,12 +8049,12 @@
       </c>
       <c r="H26" s="14">
         <f t="shared" si="0"/>
-        <v>3.0286763535893351</v>
+        <v>2.8891702111612134</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="131" t="s">
-        <v>144</v>
+      <c r="A27" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="B27" s="9">
         <v>3.84</v>
@@ -8071,7 +8065,7 @@
       <c r="D27" s="9">
         <v>3.933599781021683</v>
       </c>
-      <c r="E27" s="132">
+      <c r="E27" s="6">
         <v>0.9</v>
       </c>
       <c r="F27" s="9">
@@ -8082,12 +8076,12 @@
       </c>
       <c r="H27" s="14">
         <f t="shared" si="0"/>
-        <v>3.2632959389351712</v>
+        <v>3.2679654995208636</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="133" t="s">
-        <v>145</v>
+      <c r="A28" s="55" t="s">
+        <v>144</v>
       </c>
       <c r="B28" s="56">
         <v>4.1900000000000004</v>
@@ -8098,7 +8092,7 @@
       <c r="D28" s="56">
         <v>3.8211898948381755</v>
       </c>
-      <c r="E28" s="134">
+      <c r="E28" s="57">
         <v>0.9</v>
       </c>
       <c r="F28" s="56">
@@ -8109,12 +8103,12 @@
       </c>
       <c r="H28" s="14">
         <f t="shared" si="0"/>
-        <v>2.9164369597195896</v>
+        <v>2.9068703786437733</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="131" t="s">
-        <v>146</v>
+      <c r="A29" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="B29" s="9">
         <v>3.84</v>
@@ -8125,7 +8119,7 @@
       <c r="D29" s="9">
         <v>3.8568532687503554</v>
       </c>
-      <c r="E29" s="132">
+      <c r="E29" s="6">
         <v>1</v>
       </c>
       <c r="F29" s="9">
@@ -8136,12 +8130,12 @@
       </c>
       <c r="H29" s="14">
         <f t="shared" si="0"/>
-        <v>3.7531667360569716</v>
+        <v>3.7870359659730108</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="133" t="s">
-        <v>147</v>
+      <c r="A30" s="55" t="s">
+        <v>146</v>
       </c>
       <c r="B30" s="56">
         <v>3.84</v>
@@ -8152,7 +8146,7 @@
       <c r="D30" s="56">
         <v>3.705888348945964</v>
       </c>
-      <c r="E30" s="134">
+      <c r="E30" s="57">
         <v>1</v>
       </c>
       <c r="F30" s="56">
@@ -8163,12 +8157,12 @@
       </c>
       <c r="H30" s="14">
         <f t="shared" si="0"/>
-        <v>4.0172699125563369</v>
+        <v>4.0354377759047493</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="131" t="s">
-        <v>148</v>
+      <c r="A31" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="B31" s="9">
         <v>3.84</v>
@@ -8179,7 +8173,7 @@
       <c r="D31" s="9">
         <v>4.403895166962764</v>
       </c>
-      <c r="E31" s="132">
+      <c r="E31" s="6">
         <v>1</v>
       </c>
       <c r="F31" s="9">
@@ -8190,12 +8184,12 @@
       </c>
       <c r="H31" s="14">
         <f t="shared" si="0"/>
-        <v>3.2384358028747573</v>
+        <v>3.2654390989183613</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="133" t="s">
-        <v>149</v>
+      <c r="A32" s="55" t="s">
+        <v>148</v>
       </c>
       <c r="B32" s="56">
         <v>3.84</v>
@@ -8206,7 +8200,7 @@
       <c r="D32" s="56">
         <v>4.2165249705618049</v>
       </c>
-      <c r="E32" s="134">
+      <c r="E32" s="57">
         <v>0.9</v>
       </c>
       <c r="F32" s="56">
@@ -8217,12 +8211,12 @@
       </c>
       <c r="H32" s="14">
         <f t="shared" si="0"/>
-        <v>3.3974299200284479</v>
+        <v>3.4237295796449505</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="131" t="s">
-        <v>150</v>
+      <c r="A33" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="B33" s="9">
         <v>3.84</v>
@@ -8233,7 +8227,7 @@
       <c r="D33" s="9">
         <v>3.7417976563578033</v>
       </c>
-      <c r="E33" s="132">
+      <c r="E33" s="6">
         <v>0.9</v>
       </c>
       <c r="F33" s="9">
@@ -8244,12 +8238,12 @@
       </c>
       <c r="H33" s="14">
         <f t="shared" si="0"/>
-        <v>3.5400538784409683</v>
+        <v>3.5396501509892477</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="133" t="s">
-        <v>151</v>
+      <c r="A34" s="55" t="s">
+        <v>150</v>
       </c>
       <c r="B34" s="56">
         <v>4.26</v>
@@ -8260,7 +8254,7 @@
       <c r="D34" s="56">
         <v>4.5950509503610713</v>
       </c>
-      <c r="E34" s="134">
+      <c r="E34" s="57">
         <v>0.9</v>
       </c>
       <c r="F34" s="56">
@@ -8271,12 +8265,12 @@
       </c>
       <c r="H34" s="14">
         <f t="shared" si="0"/>
-        <v>4.1523299452316422</v>
+        <v>4.2638625447883136</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="131" t="s">
-        <v>152</v>
+      <c r="A35" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="B35" s="9">
         <v>2.78</v>
@@ -8287,7 +8281,7 @@
       <c r="D35" s="9">
         <v>4.1058377293294797</v>
       </c>
-      <c r="E35" s="132">
+      <c r="E35" s="6">
         <v>1</v>
       </c>
       <c r="F35" s="9">
@@ -8298,12 +8292,12 @@
       </c>
       <c r="H35" s="14">
         <f t="shared" si="0"/>
-        <v>2.8182441390848294</v>
+        <v>2.9172475393568167</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="133" t="s">
-        <v>154</v>
+      <c r="A36" s="55" t="s">
+        <v>153</v>
       </c>
       <c r="B36" s="56">
         <v>5.96</v>
@@ -8314,7 +8308,7 @@
       <c r="D36" s="56">
         <v>6.1593393427174998</v>
       </c>
-      <c r="E36" s="134">
+      <c r="E36" s="57">
         <v>0.9</v>
       </c>
       <c r="F36" s="56">
@@ -8325,12 +8319,12 @@
       </c>
       <c r="H36" s="14">
         <f t="shared" si="0"/>
-        <v>5.7551252183613153</v>
+        <v>5.8002882881964348</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="131" t="s">
-        <v>156</v>
+      <c r="A37" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="B37" s="9">
         <v>2.78</v>
@@ -8341,7 +8335,7 @@
       <c r="D37" s="9">
         <v>3.9736869583125203</v>
       </c>
-      <c r="E37" s="132">
+      <c r="E37" s="6">
         <v>0.9</v>
       </c>
       <c r="F37" s="9">
@@ -8352,12 +8346,12 @@
       </c>
       <c r="H37" s="14">
         <f t="shared" si="0"/>
-        <v>2.5911818550512646</v>
+        <v>2.6943684610032088</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="133" t="s">
-        <v>157</v>
+      <c r="A38" s="55" t="s">
+        <v>156</v>
       </c>
       <c r="B38" s="56">
         <v>4.1900000000000004</v>
@@ -8368,7 +8362,7 @@
       <c r="D38" s="56">
         <v>4.3655765807730429</v>
       </c>
-      <c r="E38" s="134">
+      <c r="E38" s="57">
         <v>0.9</v>
       </c>
       <c r="F38" s="56">
@@ -8379,12 +8373,12 @@
       </c>
       <c r="H38" s="14">
         <f t="shared" si="0"/>
-        <v>3.2505440308554738</v>
+        <v>3.3004338478415125</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="131" t="s">
-        <v>158</v>
+      <c r="A39" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="B39" s="9">
         <v>3.32</v>
@@ -8395,7 +8389,7 @@
       <c r="D39" s="9">
         <v>4.4086778766527672</v>
       </c>
-      <c r="E39" s="132">
+      <c r="E39" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="F39" s="9">
@@ -8406,12 +8400,12 @@
       </c>
       <c r="H39" s="14">
         <f t="shared" si="0"/>
-        <v>4.6696238902000848</v>
+        <v>4.8277641000843818</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="133" t="s">
-        <v>160</v>
+      <c r="A40" s="55" t="s">
+        <v>159</v>
       </c>
       <c r="B40" s="56">
         <v>4.1900000000000004</v>
@@ -8422,7 +8416,7 @@
       <c r="D40" s="56">
         <v>4.6380416946562937</v>
       </c>
-      <c r="E40" s="134">
+      <c r="E40" s="57">
         <v>0.9</v>
       </c>
       <c r="F40" s="56">
@@ -8433,12 +8427,12 @@
       </c>
       <c r="H40" s="14">
         <f t="shared" si="0"/>
-        <v>4.1406821373520426</v>
+        <v>4.2595261221204987</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="131" t="s">
-        <v>161</v>
+      <c r="A41" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B41" s="9">
         <v>3.32</v>
@@ -8449,7 +8443,7 @@
       <c r="D41" s="9">
         <v>4.1490866159605329</v>
       </c>
-      <c r="E41" s="132">
+      <c r="E41" s="6">
         <v>1</v>
       </c>
       <c r="F41" s="9">
@@ -8460,12 +8454,12 @@
       </c>
       <c r="H41" s="14">
         <f t="shared" si="0"/>
-        <v>3.0307873328212342</v>
+        <v>3.0951575810295084</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="133" t="s">
-        <v>162</v>
+      <c r="A42" s="55" t="s">
+        <v>161</v>
       </c>
       <c r="B42" s="56">
         <v>4.1900000000000004</v>
@@ -8476,7 +8470,7 @@
       <c r="D42" s="56">
         <v>4.1509408526411349</v>
       </c>
-      <c r="E42" s="134">
+      <c r="E42" s="57">
         <v>1</v>
       </c>
       <c r="F42" s="56">
@@ -8487,12 +8481,12 @@
       </c>
       <c r="H42" s="14">
         <f t="shared" si="0"/>
-        <v>3.4042875036727218</v>
+        <v>3.4208577739087414</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="131" t="s">
-        <v>163</v>
+      <c r="A43" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>4.1900000000000004</v>
@@ -8503,7 +8497,7 @@
       <c r="D43" s="9">
         <v>4.1203082258415957</v>
       </c>
-      <c r="E43" s="132">
+      <c r="E43" s="6">
         <v>0.9</v>
       </c>
       <c r="F43" s="9">
@@ -8514,12 +8508,12 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3.6068157509599801</v>
+        <v>3.6255446854096403</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="133" t="s">
-        <v>164</v>
+      <c r="A44" s="55" t="s">
+        <v>163</v>
       </c>
       <c r="B44" s="56">
         <v>4.1900000000000004</v>
@@ -8530,7 +8524,7 @@
       <c r="D44" s="56">
         <v>4.0604725450576815</v>
       </c>
-      <c r="E44" s="134">
+      <c r="E44" s="57">
         <v>0.9</v>
       </c>
       <c r="F44" s="56">
@@ -8541,12 +8535,12 @@
       </c>
       <c r="H44" s="14">
         <f t="shared" si="0"/>
-        <v>4.1262040854761421</v>
+        <v>4.1816337746435392</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="131" t="s">
-        <v>165</v>
+      <c r="A45" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>4.1900000000000004</v>
@@ -8557,7 +8551,7 @@
       <c r="D45" s="9">
         <v>4.0222762327087151</v>
       </c>
-      <c r="E45" s="132">
+      <c r="E45" s="6">
         <v>0.9</v>
       </c>
       <c r="F45" s="9">
@@ -8568,12 +8562,12 @@
       </c>
       <c r="H45" s="14">
         <f t="shared" si="0"/>
-        <v>3.7057463017334595</v>
+        <v>3.7474995402576194</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
-        <v>166</v>
+      <c r="A46" s="55" t="s">
+        <v>165</v>
       </c>
       <c r="B46" s="56">
         <v>4.42</v>
@@ -8584,7 +8578,7 @@
       <c r="D46" s="56">
         <v>3.6502319459771546</v>
       </c>
-      <c r="E46" s="134">
+      <c r="E46" s="57">
         <v>0.9</v>
       </c>
       <c r="F46" s="56">
@@ -8595,12 +8589,12 @@
       </c>
       <c r="H46" s="14">
         <f t="shared" si="0"/>
-        <v>4.1401865305885899</v>
+        <v>4.1701111751806836</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="131" t="s">
-        <v>168</v>
+      <c r="A47" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="B47" s="9">
         <v>3.32</v>
@@ -8611,7 +8605,7 @@
       <c r="D47" s="9">
         <v>3.9813161648332605</v>
       </c>
-      <c r="E47" s="132">
+      <c r="E47" s="6">
         <v>0.9</v>
       </c>
       <c r="F47" s="9">
@@ -8622,12 +8616,12 @@
       </c>
       <c r="H47" s="14">
         <f t="shared" si="0"/>
-        <v>3.3267691721484045</v>
+        <v>3.3633459691680576</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="133" t="s">
-        <v>169</v>
+      <c r="A48" s="55" t="s">
+        <v>168</v>
       </c>
       <c r="B48" s="56">
         <v>4.1900000000000004</v>
@@ -8638,7 +8632,7 @@
       <c r="D48" s="56">
         <v>3.965095709003819</v>
       </c>
-      <c r="E48" s="134">
+      <c r="E48" s="57">
         <v>0.9</v>
       </c>
       <c r="F48" s="56">
@@ -8649,34 +8643,34 @@
       </c>
       <c r="H48" s="14">
         <f t="shared" si="0"/>
-        <v>3.8042596472833932</v>
+        <v>3.794536341178667</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="135" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="136">
+      <c r="A49" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="101">
         <v>4.1900000000000004</v>
       </c>
-      <c r="C49" s="136">
+      <c r="C49" s="101">
         <v>4.5735709740789501</v>
       </c>
-      <c r="D49" s="136">
+      <c r="D49" s="101">
         <v>4.0692615675076942</v>
       </c>
-      <c r="E49" s="137">
+      <c r="E49" s="102">
         <v>0.9</v>
       </c>
-      <c r="F49" s="136">
+      <c r="F49" s="101">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G49" s="136">
+      <c r="G49" s="101">
         <v>0.9348282637706109</v>
       </c>
       <c r="H49" s="14">
         <f t="shared" si="0"/>
-        <v>3.9418593929063395</v>
+        <v>3.9583747280679638</v>
       </c>
     </row>
   </sheetData>
@@ -8982,8 +8976,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>143</v>
+      <c r="A18" s="52" t="s">
+        <v>40</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>56</v>
@@ -9126,369 +9120,369 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="102" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="103" t="s">
+      <c r="A27" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D27" s="104">
+      <c r="D27" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="105" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="104" t="s">
+      <c r="A28" s="76" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="75" t="s">
         <v>54</v>
       </c>
       <c r="C28" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D28" s="104">
+      <c r="D28" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="102" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="103" t="s">
+      <c r="A29" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C29" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D29" s="104">
+      <c r="D29" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="103" t="s">
+      <c r="A30" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C30" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D30" s="104">
+      <c r="D30" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="102" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" s="103" t="s">
+      <c r="A31" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C31" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D31" s="104">
+      <c r="D31" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="102" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="103" t="s">
+      <c r="A32" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C32" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D32" s="104">
+      <c r="D32" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="103" t="s">
+      <c r="A33" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="74" t="s">
         <v>57</v>
       </c>
       <c r="C33" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.84</v>
       </c>
-      <c r="D33" s="104">
+      <c r="D33" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.84</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="102" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="103" t="s">
+      <c r="A34" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="74" t="s">
         <v>62</v>
       </c>
       <c r="C34" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.26</v>
       </c>
-      <c r="D34" s="104">
+      <c r="D34" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.26</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="102" t="s">
+      <c r="A35" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="74" t="s">
         <v>152</v>
-      </c>
-      <c r="B35" s="103" t="s">
-        <v>153</v>
       </c>
       <c r="C35" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>2.78</v>
       </c>
-      <c r="D35" s="104">
+      <c r="D35" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>2.78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="74" t="s">
         <v>154</v>
-      </c>
-      <c r="B36" s="103" t="s">
-        <v>155</v>
       </c>
       <c r="C36" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>5.96</v>
       </c>
-      <c r="D36" s="104">
+      <c r="D36" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>5.96</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="102" t="s">
-        <v>156</v>
-      </c>
-      <c r="B37" s="103" t="s">
-        <v>153</v>
+      <c r="A37" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="74" t="s">
+        <v>152</v>
       </c>
       <c r="C37" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>2.78</v>
       </c>
-      <c r="D37" s="104">
+      <c r="D37" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>2.78</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="102" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="103" t="s">
+      <c r="A38" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="74" t="s">
         <v>54</v>
       </c>
       <c r="C38" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D38" s="104">
+      <c r="D38" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="102" t="s">
+      <c r="A39" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" s="74" t="s">
         <v>158</v>
-      </c>
-      <c r="B39" s="103" t="s">
-        <v>159</v>
       </c>
       <c r="C39" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.32</v>
       </c>
-      <c r="D39" s="104">
+      <c r="D39" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.32</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="102" t="s">
-        <v>160</v>
-      </c>
-      <c r="B40" s="103" t="s">
+      <c r="A40" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="74" t="s">
         <v>54</v>
       </c>
       <c r="C40" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D40" s="104">
+      <c r="D40" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="102" t="s">
-        <v>161</v>
-      </c>
-      <c r="B41" s="103" t="s">
-        <v>159</v>
+      <c r="A41" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="74" t="s">
+        <v>158</v>
       </c>
       <c r="C41" s="14">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.32</v>
       </c>
-      <c r="D41" s="104">
+      <c r="D41" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.32</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="102" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="103" t="s">
+      <c r="A42" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="104">
+      <c r="C42" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D42" s="104">
+      <c r="D42" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="102" t="s">
-        <v>163</v>
-      </c>
-      <c r="B43" s="103" t="s">
+      <c r="A43" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="104">
+      <c r="C43" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D43" s="104">
+      <c r="D43" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="102" t="s">
-        <v>164</v>
-      </c>
-      <c r="B44" s="103" t="s">
+      <c r="A44" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="104">
+      <c r="C44" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D44" s="104">
+      <c r="D44" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="102" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="103" t="s">
+      <c r="A45" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="104">
+      <c r="C45" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D45" s="104">
+      <c r="D45" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="102" t="s">
+      <c r="A46" s="73" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="B46" s="103" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="104">
+      <c r="C46" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.42</v>
       </c>
-      <c r="D46" s="104">
+      <c r="D46" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.42</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="102" t="s">
-        <v>168</v>
-      </c>
-      <c r="B47" s="103" t="s">
-        <v>159</v>
-      </c>
-      <c r="C47" s="104">
+      <c r="A47" s="73" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>3.32</v>
       </c>
-      <c r="D47" s="104">
+      <c r="D47" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>3.32</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="102" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="103" t="s">
+      <c r="A48" s="73" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="104">
+      <c r="C48" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D48" s="104">
+      <c r="D48" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="102" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="103" t="s">
+      <c r="A49" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="104">
+      <c r="C49" s="75">
         <f>VLOOKUP(Tabella15[[#This Row],[HQ Country]],'[1]Geopolitical Risk Index'!A$2:B$148,2,FALSE)</f>
         <v>4.1900000000000004</v>
       </c>
-      <c r="D49" s="104">
+      <c r="D49" s="75">
         <f>Tabella15[[#This Row],[Country Geopolitical Risk Index]]</f>
         <v>4.1900000000000004</v>
       </c>
@@ -9531,7 +9525,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -9539,7 +9533,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.3948194835522369</v>
       </c>
     </row>
@@ -9548,7 +9542,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>6.0438157732721729</v>
       </c>
     </row>
@@ -9557,7 +9551,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1049432163174231</v>
       </c>
     </row>
@@ -9566,7 +9560,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.4116251089083942</v>
       </c>
     </row>
@@ -9575,7 +9569,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.3561259320403041</v>
       </c>
     </row>
@@ -9584,7 +9578,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1002007312436222</v>
       </c>
     </row>
@@ -9593,7 +9587,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9368104426669146</v>
       </c>
     </row>
@@ -9602,7 +9596,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.0981045185174132</v>
       </c>
     </row>
@@ -9611,7 +9605,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.041123077931009</v>
       </c>
     </row>
@@ -9620,7 +9614,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0242963704895498</v>
       </c>
     </row>
@@ -9629,7 +9623,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0610136651551283</v>
       </c>
     </row>
@@ -9638,7 +9632,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0756275288239578</v>
       </c>
     </row>
@@ -9647,7 +9641,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.2124622727051149</v>
       </c>
     </row>
@@ -9656,7 +9650,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.1711360861675111</v>
       </c>
     </row>
@@ -9665,7 +9659,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.2612344608866266</v>
       </c>
     </row>
@@ -9674,7 +9668,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.5829008442437091</v>
       </c>
     </row>
@@ -9683,7 +9677,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>7.3623067404550397</v>
       </c>
     </row>
@@ -9692,7 +9686,7 @@
         <v>36</v>
       </c>
       <c r="B19" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0305108185247978</v>
       </c>
     </row>
@@ -9701,7 +9695,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.3659773288524724</v>
       </c>
     </row>
@@ -9710,7 +9704,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9318580373530141</v>
       </c>
     </row>
@@ -9719,16 +9713,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>6.3838241971610312</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="52" t="s">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="B23" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.4740648625929329</v>
       </c>
     </row>
@@ -9737,7 +9731,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0129565213980154</v>
       </c>
     </row>
@@ -9746,7 +9740,7 @@
         <v>42</v>
       </c>
       <c r="B25" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>6.2516869498945535</v>
       </c>
     </row>
@@ -9755,214 +9749,214 @@
         <v>43</v>
       </c>
       <c r="B26" s="17">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.4274332673491497</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="106" t="s">
+      <c r="A27" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.8791580319865355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.8791580319865355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="106" t="s">
+      <c r="B28" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1831268905842149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1831268905842149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="106" t="s">
+      <c r="B29" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.4586691582987594</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="77" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.4586691582987594</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="106" t="s">
+      <c r="B30" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.22866134727649</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.22866134727649</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="106" t="s">
+      <c r="B31" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.0853962459764235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="77" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.0853962459764235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="106" t="s">
+      <c r="B32" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1525922833920541</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1525922833920541</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="106" t="s">
+      <c r="B33" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.8924321492201757</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="B33" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.8924321492201757</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="106" t="s">
+      <c r="B34" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>6.3566175450562223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="77" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>6.3566175450562223</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="106" t="s">
-        <v>152</v>
-      </c>
       <c r="B35" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1328503601557962</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="106" t="s">
-        <v>154</v>
+      <c r="A36" s="77" t="s">
+        <v>153</v>
       </c>
       <c r="B36" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>6.6853668727456093</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.5554790077760652</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.5554790077760652</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="106" t="s">
+      <c r="B38" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>5.2937969388208428</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>5.2937969388208428</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="106" t="s">
-        <v>158</v>
-      </c>
       <c r="B39" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.0818320543212181</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="106" t="s">
+      <c r="A40" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>6.3684379715621473</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="77" t="s">
         <v>160</v>
       </c>
-      <c r="B40" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>6.3684379715621473</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="106" t="s">
+      <c r="B41" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.2197325701583344</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="77" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.2197325701583344</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="106" t="s">
+      <c r="B42" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.5758872007358935</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.5758872007358935</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="106" t="s">
+      <c r="B43" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.6190341572699189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.6190341572699189</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="106" t="s">
+      <c r="B44" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>5.3088983638388481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="B44" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>5.3088983638388481</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="106" t="s">
+      <c r="B45" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>5.1540152244616255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="77" t="s">
         <v>165</v>
       </c>
-      <c r="B45" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>5.1540152244616255</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="106" t="s">
-        <v>166</v>
-      </c>
       <c r="B46" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.4516845621302519</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="106" t="s">
+      <c r="A47" s="77" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.6020202113105104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.6020202113105104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="106" t="s">
+      <c r="B48" s="16">
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1450347317612328</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1450347317612328</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="106" t="s">
-        <v>170</v>
-      </c>
       <c r="B49" s="16">
-        <f>[3]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[3]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[2]!Tabella2[[#This Row],[Revenue Exposure - Intermediate Component]]*[2]!Tabella2[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.5735709740789501</v>
       </c>
     </row>
@@ -10020,442 +10014,442 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="110" t="s">
-        <v>173</v>
+      <c r="B1" s="81" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="111">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+      <c r="B2" s="82">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6316280544816539</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="109" t="s">
+      <c r="A3" s="80" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1106716078139893</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="79" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9887929880820772</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="80" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9344929060040266</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="79" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.5688829315242412</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="80" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.3947116308820906</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="79" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6252323956256634</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="80" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6667150442212542</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="108" t="s">
+      <c r="A10" s="79" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1176129573193938</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="80" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.5944548231955444</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="108" t="s">
+      <c r="A12" s="79" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.5302836098801555</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="80" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6146682939877617</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="79" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0611659887696803</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="109" t="s">
+      <c r="A15" s="80" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.5089080344231705</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="109" t="s">
+      <c r="A16" s="80" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0712097569760655</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="79" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.128863289222739</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="80" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.0690349852522134</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="80" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9528832332571699</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="109" t="s">
+      <c r="A20" s="80" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9278562154832306</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="109" t="s">
+      <c r="A21" s="80" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.9435282585906557</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="108" t="s">
+      <c r="A22" s="79" t="s">
         <v>39</v>
       </c>
       <c r="B22" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>5.1913191616373506</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="80" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6284874314308784</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="108" t="s">
+      <c r="A24" s="79" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6069583492655704</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="109" t="s">
+      <c r="A25" s="80" t="s">
         <v>42</v>
       </c>
       <c r="B25" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.938256025170499</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="108" t="s">
+      <c r="A26" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="112">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+      <c r="B26" s="83">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6885977422381564</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="109" t="s">
+      <c r="A27" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.933599781021683</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.933599781021683</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="108" t="s">
+      <c r="B28" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.8211898948381755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.8211898948381755</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="109" t="s">
+      <c r="B29" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.8568532687503554</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.8568532687503554</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="108" t="s">
+      <c r="B30" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.705888348945964</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.705888348945964</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="109" t="s">
+      <c r="B31" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.403895166962764</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="80" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.403895166962764</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="109" t="s">
+      <c r="B32" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.2165249705618049</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.2165249705618049</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="109" t="s">
+      <c r="B33" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.7417976563578033</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="B33" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.7417976563578033</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="109" t="s">
+      <c r="B34" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.5950509503610713</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.5950509503610713</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="109" t="s">
-        <v>152</v>
-      </c>
       <c r="B35" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.1058377293294797</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="108" t="s">
-        <v>154</v>
+      <c r="A36" s="79" t="s">
+        <v>153</v>
       </c>
       <c r="B36" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>6.1593393427174998</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="109" t="s">
+      <c r="A37" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.9736869583125203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.9736869583125203</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="108" t="s">
+      <c r="B38" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.3655765807730429</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.3655765807730429</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="109" t="s">
-        <v>158</v>
-      </c>
       <c r="B39" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.4086778766527672</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="108" t="s">
+      <c r="A40" s="79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.6380416946562937</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="B40" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.6380416946562937</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="109" t="s">
+      <c r="B41" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1490866159605329</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1490866159605329</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="108" t="s">
+      <c r="B42" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1509408526411349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1509408526411349</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="109" t="s">
+      <c r="B43" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.1203082258415957</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.1203082258415957</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="108" t="s">
+      <c r="B44" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.0604725450576815</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="80" t="s">
         <v>164</v>
       </c>
-      <c r="B44" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.0604725450576815</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="109" t="s">
+      <c r="B45" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>4.0222762327087151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="B45" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>4.0222762327087151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="109" t="s">
-        <v>166</v>
-      </c>
       <c r="B46" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>3.6502319459771546</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="109" t="s">
+      <c r="A47" s="80" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.9813161648332605</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.9813161648332605</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="108" t="s">
+      <c r="B48" s="19">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+        <v>3.965095709003819</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="19">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
-        <v>3.965095709003819</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="109" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="112">
-        <f>[2]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[2]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
+      <c r="B49" s="83">
+        <f>[3]!Tabella26[[#This Row],[Supply Chain Exposure - Intermediate Component]]*[3]!Tabella26[[#This Row],[HHI Index - Submultiplier]]</f>
         <v>4.0692615675076942</v>
       </c>
     </row>
@@ -10500,14 +10494,14 @@
         <v>64</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="113">
+      <c r="B2" s="84">
         <v>1.45</v>
       </c>
       <c r="C2" s="51">
@@ -10519,7 +10513,7 @@
       <c r="A3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="113">
+      <c r="B3" s="84">
         <v>0.35</v>
       </c>
       <c r="C3" s="51">
@@ -10531,7 +10525,7 @@
       <c r="A4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="113">
+      <c r="B4" s="84">
         <v>-0.35</v>
       </c>
       <c r="C4" s="51">
@@ -10543,7 +10537,7 @@
       <c r="A5" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113">
+      <c r="B5" s="84">
         <v>-0.72</v>
       </c>
       <c r="C5" s="51">
@@ -10555,7 +10549,7 @@
       <c r="A6" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="113">
+      <c r="B6" s="84">
         <v>5.0999999999999996</v>
       </c>
       <c r="C6" s="51">
@@ -10567,7 +10561,7 @@
       <c r="A7" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="113">
+      <c r="B7" s="84">
         <v>2.15</v>
       </c>
       <c r="C7" s="51">
@@ -10579,7 +10573,7 @@
       <c r="A8" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="113">
+      <c r="B8" s="84">
         <v>1.69</v>
       </c>
       <c r="C8" s="51">
@@ -10591,7 +10585,7 @@
       <c r="A9" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="113">
+      <c r="B9" s="84">
         <v>-0.57999999999999996</v>
       </c>
       <c r="C9" s="51">
@@ -10603,7 +10597,7 @@
       <c r="A10" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="113">
+      <c r="B10" s="84">
         <v>-0.56999999999999995</v>
       </c>
       <c r="C10" s="51">
@@ -10615,7 +10609,7 @@
       <c r="A11" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="113">
+      <c r="B11" s="84">
         <v>0.44</v>
       </c>
       <c r="C11" s="51">
@@ -10627,7 +10621,7 @@
       <c r="A12" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="113">
+      <c r="B12" s="84">
         <v>1.02</v>
       </c>
       <c r="C12" s="51">
@@ -10639,7 +10633,7 @@
       <c r="A13" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="113">
+      <c r="B13" s="84">
         <v>-0.32</v>
       </c>
       <c r="C13" s="51">
@@ -10651,7 +10645,7 @@
       <c r="A14" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="113">
+      <c r="B14" s="84">
         <v>0.16</v>
       </c>
       <c r="C14" s="51">
@@ -10663,7 +10657,7 @@
       <c r="A15" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="113">
+      <c r="B15" s="84">
         <v>0.52</v>
       </c>
       <c r="C15" s="51">
@@ -10675,7 +10669,7 @@
       <c r="A16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="113">
+      <c r="B16" s="84">
         <v>-0.39</v>
       </c>
       <c r="C16" s="51">
@@ -10687,7 +10681,7 @@
       <c r="A17" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="113">
+      <c r="B17" s="84">
         <v>1.1000000000000001</v>
       </c>
       <c r="C17" s="51">
@@ -10699,7 +10693,7 @@
       <c r="A18" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="113">
+      <c r="B18" s="84">
         <v>0.87</v>
       </c>
       <c r="C18" s="51">
@@ -10711,7 +10705,7 @@
       <c r="A19" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="113">
+      <c r="B19" s="84">
         <v>-1.24</v>
       </c>
       <c r="C19" s="51">
@@ -10723,7 +10717,7 @@
       <c r="A20" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="113">
+      <c r="B20" s="84">
         <v>-0.02</v>
       </c>
       <c r="C20" s="51">
@@ -10735,7 +10729,7 @@
       <c r="A21" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="113">
+      <c r="B21" s="84">
         <v>0.76</v>
       </c>
       <c r="C21" s="51">
@@ -10747,7 +10741,7 @@
       <c r="A22" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="113">
+      <c r="B22" s="84">
         <v>0.06</v>
       </c>
       <c r="C22" s="51">
@@ -10756,10 +10750,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A23" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="113">
+      <c r="A23" s="136" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="84">
         <v>0.44</v>
       </c>
       <c r="C23" s="51">
@@ -10771,7 +10765,7 @@
       <c r="A24" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="113">
+      <c r="B24" s="84">
         <v>-1.17</v>
       </c>
       <c r="C24" s="51">
@@ -10783,7 +10777,7 @@
       <c r="A25" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="113">
+      <c r="B25" s="84">
         <v>-0.69</v>
       </c>
       <c r="C25" s="51">
@@ -10795,7 +10789,7 @@
       <c r="A26" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="113">
+      <c r="B26" s="84">
         <v>-1</v>
       </c>
       <c r="C26" s="51">
@@ -10805,9 +10799,9 @@
     </row>
     <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A27" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="114">
+        <v>143</v>
+      </c>
+      <c r="B27" s="85">
         <v>0.9</v>
       </c>
       <c r="C27" s="51">
@@ -10816,10 +10810,10 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A28" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28" s="114">
+      <c r="A28" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="85">
         <v>1.6</v>
       </c>
       <c r="C28" s="51">
@@ -10829,9 +10823,9 @@
     </row>
     <row r="29" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A29" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="114">
+        <v>145</v>
+      </c>
+      <c r="B29" s="85">
         <v>2.2000000000000002</v>
       </c>
       <c r="C29" s="51">
@@ -10840,10 +10834,10 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A30" s="115" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="114">
+      <c r="A30" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="85">
         <v>3.5</v>
       </c>
       <c r="C30" s="51">
@@ -10853,9 +10847,9 @@
     </row>
     <row r="31" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A31" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" s="114">
+        <v>147</v>
+      </c>
+      <c r="B31" s="85">
         <v>2.8</v>
       </c>
       <c r="C31" s="51">
@@ -10864,10 +10858,10 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A32" s="115" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="114">
+      <c r="A32" s="86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="85">
         <v>0</v>
       </c>
       <c r="C32" s="51">
@@ -10877,9 +10871,9 @@
     </row>
     <row r="33" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A33" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="114">
+        <v>149</v>
+      </c>
+      <c r="B33" s="85">
         <v>0.3</v>
       </c>
       <c r="C33" s="51">
@@ -10888,10 +10882,10 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A34" s="115" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="114">
+      <c r="A34" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="85">
         <v>1</v>
       </c>
       <c r="C34" s="51">
@@ -10901,9 +10895,9 @@
     </row>
     <row r="35" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="B35" s="114">
+        <v>151</v>
+      </c>
+      <c r="B35" s="85">
         <v>2.2000000000000002</v>
       </c>
       <c r="C35" s="51">
@@ -10912,10 +10906,10 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A36" s="115" t="s">
-        <v>154</v>
-      </c>
-      <c r="B36" s="114">
+      <c r="A36" s="86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="85">
         <v>0.2</v>
       </c>
       <c r="C36" s="51">
@@ -10925,9 +10919,9 @@
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="B37" s="114">
+        <v>155</v>
+      </c>
+      <c r="B37" s="85">
         <v>1.3</v>
       </c>
       <c r="C37" s="51">
@@ -10936,10 +10930,10 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A38" s="115" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="114">
+      <c r="A38" s="86" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="85">
         <v>0.3</v>
       </c>
       <c r="C38" s="51">
@@ -10949,9 +10943,9 @@
     </row>
     <row r="39" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A39" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="B39" s="114">
+        <v>157</v>
+      </c>
+      <c r="B39" s="85">
         <v>4.5999999999999996</v>
       </c>
       <c r="C39" s="51">
@@ -10960,10 +10954,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A40" s="115" t="s">
-        <v>160</v>
-      </c>
-      <c r="B40" s="114">
+      <c r="A40" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="85">
         <v>1.5</v>
       </c>
       <c r="C40" s="51">
@@ -10973,9 +10967,9 @@
     </row>
     <row r="41" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A41" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="B41" s="114">
+        <v>160</v>
+      </c>
+      <c r="B41" s="85">
         <v>2.5</v>
       </c>
       <c r="C41" s="51">
@@ -10984,10 +10978,10 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
-        <v>162</v>
-      </c>
-      <c r="B42" s="114">
+      <c r="A42" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="85">
         <v>2.4</v>
       </c>
       <c r="C42" s="51">
@@ -10997,9 +10991,9 @@
     </row>
     <row r="43" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="B43" s="114">
+        <v>162</v>
+      </c>
+      <c r="B43" s="85">
         <v>1.8</v>
       </c>
       <c r="C43" s="51">
@@ -11008,10 +11002,10 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A44" s="115" t="s">
-        <v>164</v>
-      </c>
-      <c r="B44" s="114">
+      <c r="A44" s="86" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="85">
         <v>0.1</v>
       </c>
       <c r="C44" s="51">
@@ -11021,9 +11015,9 @@
     </row>
     <row r="45" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A45" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="114">
+        <v>164</v>
+      </c>
+      <c r="B45" s="85">
         <v>1.8</v>
       </c>
       <c r="C45" s="51">
@@ -11032,10 +11026,10 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A46" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="B46" s="114">
+      <c r="A46" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="85">
         <v>0.3</v>
       </c>
       <c r="C46" s="51">
@@ -11045,9 +11039,9 @@
     </row>
     <row r="47" spans="1:3" ht="19" x14ac:dyDescent="0.25">
       <c r="A47" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="B47" s="114">
+        <v>167</v>
+      </c>
+      <c r="B47" s="85">
         <v>0.6</v>
       </c>
       <c r="C47" s="51">
@@ -11056,10 +11050,10 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A48" s="115" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="114">
+      <c r="A48" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="85">
         <v>0.8</v>
       </c>
       <c r="C48" s="51">
@@ -11068,13 +11062,13 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="19" x14ac:dyDescent="0.25">
-      <c r="A49" s="116" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="114">
+      <c r="A49" s="87" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="85">
         <v>0.4</v>
       </c>
-      <c r="C49" s="116">
+      <c r="C49" s="87">
         <f xml:space="preserve"> IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;0, 0.8,IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;2, 0.9, IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]] &lt; 4, 1,IF(Tabella110[[#This Row],[Net Debt/EBITDA 2024]]&lt;6,1.1,1.2))))</f>
         <v>0.9</v>
       </c>
@@ -11121,20 +11115,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="135" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="101"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
+      <c r="A2" s="135"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
     </row>
     <row r="4" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -11143,19 +11137,19 @@
       <c r="B4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="117" t="s">
+      <c r="E4" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="117" t="s">
+      <c r="F4" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="117" t="s">
+      <c r="G4" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="118" t="s">
+      <c r="H4" s="89" t="s">
         <v>73</v>
       </c>
     </row>
@@ -11166,21 +11160,20 @@
       <c r="B5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="120" t="s">
+      <c r="E5" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G5" s="120">
+      <c r="F5" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="91">
         <f t="shared" ref="G5:G52" si="0">IF(F5="Very low risk",1,IF(F5="Low risk",2,IF(F5="Intermediate risk",3,IF(F5="Moderately high risk",4,IF(F5="High risk",5,IF(F5="Very high risk",6, ""))))))</f>
         <v>4</v>
       </c>
-      <c r="H5" s="119">
+      <c r="H5" s="90">
         <f t="shared" ref="H5:H52" si="1">IF(F5="Very low risk",0.75,IF(F5="Low risk",0.85,IF(F5="Intermediate risk",1,IF(F5="Moderately high risk",1.1,IF(F5="High risk",1.15,IF(F5="Very high risk",1.25, ""))))))</f>
         <v>1.1000000000000001</v>
       </c>
@@ -11192,21 +11185,20 @@
       <c r="B6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="120" t="s">
+      <c r="E6" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G6" s="120">
+      <c r="F6" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H6" s="119">
+      <c r="H6" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11218,21 +11210,20 @@
       <c r="B7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="120" t="s">
+      <c r="E7" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G7" s="120">
+      <c r="F7" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H7" s="119">
+      <c r="H7" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11244,21 +11235,20 @@
       <c r="B8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="119" t="s">
+      <c r="D8" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="120" t="s">
+      <c r="E8" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G8" s="120">
+      <c r="F8" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H8" s="119">
+      <c r="H8" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11270,21 +11260,20 @@
       <c r="B9" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="119" t="s">
+      <c r="D9" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G9" s="120">
+      <c r="F9" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H9" s="119">
+      <c r="H9" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11296,21 +11285,20 @@
       <c r="B10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="120" t="s">
+      <c r="E10" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G10" s="120">
+      <c r="F10" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H10" s="119">
+      <c r="H10" s="90">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11322,21 +11310,20 @@
       <c r="B11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="121" t="s">
+      <c r="E11" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G11" s="120">
+      <c r="F11" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H11" s="119">
+      <c r="H11" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11348,21 +11335,20 @@
       <c r="B12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="120" t="s">
+      <c r="E12" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G12" s="120">
+      <c r="F12" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H12" s="119">
+      <c r="H12" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11374,21 +11360,20 @@
       <c r="B13" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="119" t="s">
+      <c r="D13" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="120" t="s">
+      <c r="E13" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G13" s="120">
+      <c r="F13" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H13" s="119">
+      <c r="H13" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11400,21 +11385,20 @@
       <c r="B14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="D14" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="120" t="s">
+      <c r="E14" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G14" s="120">
+      <c r="F14" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H14" s="119">
+      <c r="H14" s="90">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11426,21 +11410,20 @@
       <c r="B15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="120" t="s">
+      <c r="E15" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G15" s="120">
+      <c r="F15" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H15" s="119">
+      <c r="H15" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11452,21 +11435,20 @@
       <c r="B16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="120" t="s">
+      <c r="E16" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G16" s="120">
+      <c r="F16" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H16" s="119">
+      <c r="H16" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11478,21 +11460,20 @@
       <c r="B17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="120" t="s">
+      <c r="E17" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G17" s="120">
+      <c r="F17" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H17" s="119">
+      <c r="H17" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11504,21 +11485,20 @@
       <c r="B18" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="120" t="s">
+      <c r="E18" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G18" s="120">
+      <c r="F18" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H18" s="119">
+      <c r="H18" s="90">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11530,21 +11510,20 @@
       <c r="B19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="120" t="s">
+      <c r="E19" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G19" s="120">
+      <c r="F19" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H19" s="119">
+      <c r="H19" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11556,21 +11535,20 @@
       <c r="B20" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="119" t="s">
+      <c r="D20" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="120" t="s">
+      <c r="E20" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G20" s="120">
+      <c r="F20" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H20" s="119">
+      <c r="H20" s="90">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11582,21 +11560,20 @@
       <c r="B21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="120" t="s">
+      <c r="E21" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G21" s="120">
+      <c r="F21" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H21" s="119">
+      <c r="H21" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11608,21 +11585,20 @@
       <c r="B22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="119" t="s">
+      <c r="D22" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="120" t="s">
+      <c r="E22" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G22" s="120">
+      <c r="F22" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H22" s="119">
+      <c r="H22" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11634,21 +11610,20 @@
       <c r="B23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="119" t="s">
+      <c r="D23" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="120" t="s">
+      <c r="E23" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G23" s="120">
+      <c r="F23" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H23" s="119">
+      <c r="H23" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11660,21 +11635,20 @@
       <c r="B24" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="119" t="s">
+      <c r="D24" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="120" t="s">
+      <c r="E24" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G24" s="120">
+      <c r="F24" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H24" s="119">
+      <c r="H24" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11686,21 +11660,20 @@
       <c r="B25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="119" t="s">
+      <c r="D25" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G25" s="120">
+      <c r="F25" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H25" s="119">
+      <c r="H25" s="90">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11712,21 +11685,20 @@
       <c r="B26" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="119" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="120" t="s">
+      <c r="D26" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F26" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G26" s="120">
+      <c r="F26" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H26" s="119">
+      <c r="H26" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11738,21 +11710,20 @@
       <c r="B27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="119" t="s">
+      <c r="D27" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="120" t="s">
+      <c r="E27" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G27" s="120">
+      <c r="F27" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H27" s="119">
+      <c r="H27" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11764,21 +11735,20 @@
       <c r="B28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="119" t="s">
+      <c r="D28" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="120" t="s">
+      <c r="E28" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G28" s="120">
+      <c r="F28" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H28" s="119">
+      <c r="H28" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11790,21 +11760,20 @@
       <c r="B29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="119" t="s">
+      <c r="D29" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="120" t="s">
+      <c r="E29" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G29" s="120">
+      <c r="F29" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H29" s="119">
+      <c r="H29" s="90">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11816,21 +11785,20 @@
       <c r="B30" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="122" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" s="120" t="s">
+      <c r="D30" s="93" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G30" s="120">
+      <c r="F30" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H30" s="123">
+      <c r="H30" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11842,21 +11810,20 @@
       <c r="B31" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="120" t="s">
+      <c r="D31" s="95" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G31" s="120">
+      <c r="F31" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H31" s="123">
+      <c r="H31" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11868,21 +11835,20 @@
       <c r="B32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="122" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32" s="120" t="s">
+      <c r="D32" s="93" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="F32" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G32" s="120">
+      <c r="F32" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H32" s="123">
+      <c r="H32" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11894,21 +11860,20 @@
       <c r="B33" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="124" t="s">
-        <v>147</v>
-      </c>
-      <c r="E33" s="120" t="s">
+      <c r="D33" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G33" s="120">
+      <c r="F33" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H33" s="123">
+      <c r="H33" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11920,21 +11885,20 @@
       <c r="B34" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D34" s="122" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34" s="120" t="s">
+      <c r="D34" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G34" s="120">
+      <c r="F34" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H34" s="123">
+      <c r="H34" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -11946,21 +11910,20 @@
       <c r="B35" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="124" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35" s="120" t="s">
+      <c r="D35" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G35" s="120">
+      <c r="F35" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H35" s="123">
+      <c r="H35" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -11972,21 +11935,20 @@
       <c r="B36" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="122" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="120" t="s">
+      <c r="D36" s="93" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G36" s="120">
+      <c r="F36" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H36" s="123">
+      <c r="H36" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -11998,21 +11960,20 @@
       <c r="B37" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="124" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" s="120" t="s">
+      <c r="D37" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G37" s="120">
+      <c r="F37" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H37" s="123">
+      <c r="H37" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -12024,21 +11985,20 @@
       <c r="B38" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="122" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38" s="120" t="s">
+      <c r="D38" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F38" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G38" s="120">
+      <c r="F38" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H38" s="123">
+      <c r="H38" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -12050,21 +12010,20 @@
       <c r="B39" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="124" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="120" t="s">
+      <c r="D39" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F39" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G39" s="120">
+      <c r="F39" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H39" s="123">
+      <c r="H39" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12076,21 +12035,20 @@
       <c r="B40" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="122" t="s">
-        <v>156</v>
-      </c>
-      <c r="E40" s="120" t="s">
+      <c r="D40" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G40" s="120">
+      <c r="F40" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G40" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H40" s="123">
+      <c r="H40" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -12102,21 +12060,20 @@
       <c r="B41" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="124" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" s="120" t="s">
+      <c r="D41" s="95" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F41" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G41" s="120">
+      <c r="F41" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H41" s="123">
+      <c r="H41" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -12128,21 +12085,20 @@
       <c r="B42" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="122" t="s">
-        <v>158</v>
-      </c>
-      <c r="E42" s="120" t="s">
+      <c r="D42" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="F42" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G42" s="120">
+      <c r="F42" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H42" s="123">
+      <c r="H42" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12154,21 +12110,20 @@
       <c r="B43" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="124" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="120" t="s">
+      <c r="D43" s="95" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G43" s="120">
+      <c r="F43" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H43" s="123">
+      <c r="H43" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -12180,21 +12135,20 @@
       <c r="B44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="122" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" s="120" t="s">
+      <c r="D44" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G44" s="120">
+      <c r="F44" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H44" s="123">
+      <c r="H44" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -12206,21 +12160,20 @@
       <c r="B45" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="124" t="s">
-        <v>162</v>
-      </c>
-      <c r="E45" s="120" t="s">
+      <c r="D45" s="95" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="F45" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Low risk</v>
-      </c>
-      <c r="G45" s="120">
+      <c r="F45" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="91">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H45" s="123">
+      <c r="H45" s="94">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
@@ -12232,21 +12185,20 @@
       <c r="B46" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="122" t="s">
-        <v>163</v>
-      </c>
-      <c r="E46" s="120" t="s">
+      <c r="D46" s="93" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="F46" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G46" s="120">
+      <c r="F46" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H46" s="123">
+      <c r="H46" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -12258,21 +12210,20 @@
       <c r="B47" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="124" t="s">
-        <v>164</v>
-      </c>
-      <c r="E47" s="120" t="s">
+      <c r="D47" s="95" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G47" s="120">
+      <c r="F47" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H47" s="123">
+      <c r="H47" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12284,21 +12235,20 @@
       <c r="B48" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="122" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" s="120" t="s">
+      <c r="D48" s="93" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="F48" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Intermediate risk</v>
-      </c>
-      <c r="G48" s="120">
+      <c r="F48" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" s="91">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H48" s="123">
+      <c r="H48" s="94">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -12310,21 +12260,20 @@
       <c r="B49" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="124" t="s">
-        <v>166</v>
-      </c>
-      <c r="E49" s="120" t="s">
+      <c r="D49" s="95" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G49" s="120">
+      <c r="F49" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H49" s="123">
+      <c r="H49" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12336,21 +12285,20 @@
       <c r="B50" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="122" t="s">
-        <v>168</v>
-      </c>
-      <c r="E50" s="120" t="s">
+      <c r="D50" s="93" t="s">
+        <v>167</v>
+      </c>
+      <c r="E50" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F50" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G50" s="120">
+      <c r="F50" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H50" s="123">
+      <c r="H50" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12362,21 +12310,20 @@
       <c r="B51" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="124" t="s">
-        <v>169</v>
-      </c>
-      <c r="E51" s="120" t="s">
+      <c r="D51" s="95" t="s">
+        <v>168</v>
+      </c>
+      <c r="E51" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="F51" s="119" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G51" s="120">
+      <c r="F51" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="91">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H51" s="123">
+      <c r="H51" s="94">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12388,21 +12335,20 @@
       <c r="B52" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D52" s="125" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="126" t="s">
+      <c r="D52" s="96" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="F52" s="127" t="str">
-        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],[4]!Tabella1[#Data],2)</f>
-        <v>Moderately high risk</v>
-      </c>
-      <c r="G52" s="126">
+      <c r="F52" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="97">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H52" s="128">
+      <c r="H52" s="99">
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
@@ -12510,19 +12456,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="135" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
+      <c r="A2" s="135"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
@@ -64584,12 +64530,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="efa000e167d9ce5db8cd2eb5b6f87cd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f94584ddf2c7798ba84aeef6e679263" ns2:_="">
     <xsd:import namespace="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
@@ -64727,7 +64667,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -64736,23 +64676,13 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D57F7E9-094C-4E40-AC1D-B397B1E486C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC01572-DE87-4099-A912-442FA7F15803}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -64770,10 +64700,26 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6D44B9-BFA0-496F-91FF-88181837C605}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D57F7E9-094C-4E40-AC1D-B397B1E486C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>